--- a/followingmatrix.xlsx
+++ b/followingmatrix.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anavas\Desktop\Análisis ANG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE0FC2EE-9373-4411-AEBC-E14DEF66BA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699773A4-C380-4385-886F-E637BB406AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF2AE531-21D2-45B6-A564-3BA4CEACDF38}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AB$129</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3359,8 +3362,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;Q&quot;* #,##0.00_-;\-&quot;Q&quot;* #,##0.00_-;_-&quot;Q&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000000"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="32" x14ac:knownFonts="1">
     <font>
@@ -3740,13 +3743,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3793,13 +3797,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3823,22 +3827,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3850,16 +3848,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3871,17 +3866,14 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3892,43 +3884,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3952,13 +3941,10 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3979,12 +3965,32 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
+  <cellStyles count="5">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{FB3010D3-CA1D-470F-8BBC-29235B0BC91E}"/>
-    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
+    <cellStyle name="Normal 2" xfId="4" xr:uid="{FB3010D3-CA1D-470F-8BBC-29235B0BC91E}"/>
+    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4341,8 +4347,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A11FCA36-68E1-48DB-B35D-1906B0292A5D}">
   <dimension ref="A1:AB129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="72.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="215" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" style="78" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5703125" style="78" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="117" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="78" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4388,10 +4423,10 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="72" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="4" t="s">
@@ -4428,7 +4463,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -4475,10 +4510,10 @@
       <c r="O2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="73">
         <v>15.579159300000001</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="73">
         <v>-89.976387500000001</v>
       </c>
       <c r="R2" s="14">
@@ -4517,7 +4552,7 @@
         <v>628193.04</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -4564,10 +4599,10 @@
       <c r="O3" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="P3" s="13">
+      <c r="P3" s="73">
         <v>15.4598551</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="73">
         <v>-90.397120799999996</v>
       </c>
       <c r="R3" s="14">
@@ -4607,7 +4642,7 @@
         <v>5162058.6700000009</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -4654,10 +4689,10 @@
       <c r="O4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="73">
         <v>14.616725499999999</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="73">
         <v>-89.621947899999995</v>
       </c>
       <c r="R4" s="14">
@@ -4697,7 +4732,7 @@
         <v>751578.17000000086</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -4744,10 +4779,10 @@
       <c r="O5" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="73">
         <v>14.5636609</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="73">
         <v>-89.337200699999997</v>
       </c>
       <c r="R5" s="14">
@@ -4786,7 +4821,7 @@
         <v>7669895.1700000018</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -4833,10 +4868,10 @@
       <c r="O6" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="73">
         <v>14.7658588</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6" s="73">
         <v>-90.291815799999995</v>
       </c>
       <c r="R6" s="14">
@@ -4875,7 +4910,7 @@
         <v>4403897.18</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="273" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -4922,10 +4957,10 @@
       <c r="O7" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="P7" s="23">
+      <c r="P7" s="74">
         <v>14.402914900000001</v>
       </c>
-      <c r="Q7" s="23">
+      <c r="Q7" s="74">
         <v>-90.715337399999996</v>
       </c>
       <c r="R7" s="24">
@@ -5010,10 +5045,10 @@
       <c r="O8" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="74">
         <v>14.3309</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="74">
         <v>-91.212999999999994</v>
       </c>
       <c r="R8" s="24">
@@ -5052,7 +5087,7 @@
         <v>5712762.1600000001</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="273" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -5099,22 +5134,22 @@
       <c r="O9" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="P9" s="13">
+      <c r="P9" s="73">
         <v>14.537479899999999</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="Q9" s="73">
         <v>-90.636207299999995</v>
       </c>
-      <c r="R9" s="29">
+      <c r="R9" s="28">
         <v>45107</v>
       </c>
-      <c r="S9" s="29">
+      <c r="S9" s="28">
         <v>45346</v>
       </c>
-      <c r="T9" s="30">
+      <c r="T9" s="29">
         <v>240</v>
       </c>
-      <c r="U9" s="30">
+      <c r="U9" s="29">
         <v>240</v>
       </c>
       <c r="V9" s="15" t="s">
@@ -5141,7 +5176,7 @@
         <v>19002770.43</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -5188,10 +5223,10 @@
       <c r="O10" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="P10" s="23">
+      <c r="P10" s="74">
         <v>14.5742718</v>
       </c>
-      <c r="Q10" s="23">
+      <c r="Q10" s="74">
         <v>-90.527205800000004</v>
       </c>
       <c r="R10" s="24">
@@ -5230,7 +5265,7 @@
         <v>172479.79999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="273" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -5277,10 +5312,10 @@
       <c r="O11" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="P11" s="23">
+      <c r="P11" s="74">
         <v>15.491871099999999</v>
       </c>
-      <c r="Q11" s="23">
+      <c r="Q11" s="74">
         <v>-91.757156199999997</v>
       </c>
       <c r="R11" s="24">
@@ -5319,7 +5354,7 @@
         <v>8739769.599999994</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -5366,10 +5401,10 @@
       <c r="O12" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="P12" s="31">
+      <c r="P12" s="73">
         <v>15.321685</v>
       </c>
-      <c r="Q12" s="31">
+      <c r="Q12" s="73">
         <v>-91.484628999999998</v>
       </c>
       <c r="R12" s="14">
@@ -5408,7 +5443,7 @@
         <v>2512620.25</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="356.25" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -5440,7 +5475,7 @@
       <c r="J13" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="K13" s="32" t="s">
+      <c r="K13" s="30" t="s">
         <v>126</v>
       </c>
       <c r="L13" s="11" t="s">
@@ -5455,10 +5490,10 @@
       <c r="O13" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="P13" s="13">
+      <c r="P13" s="73">
         <v>15.450245499999999</v>
       </c>
-      <c r="Q13" s="13">
+      <c r="Q13" s="73">
         <v>-88.861024799999996</v>
       </c>
       <c r="R13" s="14">
@@ -5497,7 +5532,7 @@
         <v>38067790.539999999</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="318.75" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -5529,7 +5564,7 @@
       <c r="J14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="31" t="s">
         <v>134</v>
       </c>
       <c r="L14" s="11" t="s">
@@ -5544,10 +5579,10 @@
       <c r="O14" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="P14" s="13">
+      <c r="P14" s="73">
         <v>15.737015899999999</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="Q14" s="73">
         <v>-88.597672599999996</v>
       </c>
       <c r="R14" s="14">
@@ -5587,7 +5622,7 @@
         <v>42903219.769999996</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" ht="337.5" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -5619,7 +5654,7 @@
       <c r="J15" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="K15" s="32" t="s">
+      <c r="K15" s="30" t="s">
         <v>142</v>
       </c>
       <c r="L15" s="11" t="s">
@@ -5634,10 +5669,10 @@
       <c r="O15" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="P15" s="13">
+      <c r="P15" s="73">
         <v>13.871774500000001</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="Q15" s="73">
         <v>-90.096409199999997</v>
       </c>
       <c r="R15" s="14">
@@ -5677,7 +5712,7 @@
         <v>38080563.010000005</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" ht="273" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -5709,7 +5744,7 @@
       <c r="J16" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="K16" s="34" t="s">
+      <c r="K16" s="32" t="s">
         <v>150</v>
       </c>
       <c r="L16" s="11" t="s">
@@ -5724,10 +5759,10 @@
       <c r="O16" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="P16" s="13">
+      <c r="P16" s="73">
         <v>16.7967154</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="Q16" s="73">
         <v>-90.096540599999997</v>
       </c>
       <c r="R16" s="14">
@@ -5767,7 +5802,7 @@
         <v>6267564.4800000042</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="356.25" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -5799,7 +5834,7 @@
       <c r="J17" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="K17" s="32" t="s">
+      <c r="K17" s="30" t="s">
         <v>157</v>
       </c>
       <c r="L17" s="11" t="s">
@@ -5814,10 +5849,10 @@
       <c r="O17" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="P17" s="31">
+      <c r="P17" s="73">
         <v>16.929711999999999</v>
       </c>
-      <c r="Q17" s="31">
+      <c r="Q17" s="73">
         <v>-89.955291099999997</v>
       </c>
       <c r="R17" s="14">
@@ -5856,7 +5891,7 @@
         <v>224030892.52000001</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="337.5" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -5888,7 +5923,7 @@
       <c r="J18" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="K18" s="33" t="s">
+      <c r="K18" s="31" t="s">
         <v>164</v>
       </c>
       <c r="L18" s="11" t="s">
@@ -5903,10 +5938,10 @@
       <c r="O18" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="P18" s="12">
+      <c r="P18" s="75">
         <v>16.922133599999999</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="Q18" s="75">
         <v>-89.895841799999999</v>
       </c>
       <c r="R18" s="14">
@@ -5946,7 +5981,7 @@
         <v>5921093.9399999995</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="318.75" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -5968,7 +6003,7 @@
       <c r="G19" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="33">
         <v>0.24579999999999999</v>
       </c>
       <c r="I19" s="10">
@@ -5978,7 +6013,7 @@
       <c r="J19" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="K19" s="32" t="s">
+      <c r="K19" s="30" t="s">
         <v>173</v>
       </c>
       <c r="L19" s="11" t="s">
@@ -5993,10 +6028,10 @@
       <c r="O19" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="P19" s="13">
+      <c r="P19" s="73">
         <v>14.702806600000001</v>
       </c>
-      <c r="Q19" s="13">
+      <c r="Q19" s="73">
         <v>-91.896000900000004</v>
       </c>
       <c r="R19" s="14">
@@ -6035,7 +6070,7 @@
         <v>198066194.37</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="300" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -6067,7 +6102,7 @@
       <c r="J20" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="K20" s="32" t="s">
+      <c r="K20" s="30" t="s">
         <v>179</v>
       </c>
       <c r="L20" s="11" t="s">
@@ -6082,10 +6117,10 @@
       <c r="O20" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="P20" s="13">
+      <c r="P20" s="73">
         <v>14.8550653</v>
       </c>
-      <c r="Q20" s="13">
+      <c r="Q20" s="73">
         <v>-91.510258500000006</v>
       </c>
       <c r="R20" s="14">
@@ -6125,7 +6160,7 @@
         <v>3978783.8299999991</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -6172,10 +6207,10 @@
       <c r="O21" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="73">
         <v>15.989296</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="73">
         <v>-90.778386600000005</v>
       </c>
       <c r="R21" s="14">
@@ -6214,7 +6249,7 @@
         <v>127603.41999999993</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -6261,10 +6296,10 @@
       <c r="O22" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="P22" s="36">
+      <c r="P22" s="75">
         <v>15.28</v>
       </c>
-      <c r="Q22" s="36">
+      <c r="Q22" s="75">
         <v>-91.144300000000001</v>
       </c>
       <c r="R22" s="14">
@@ -6279,7 +6314,7 @@
       <c r="U22" s="7">
         <v>120</v>
       </c>
-      <c r="V22" s="37" t="s">
+      <c r="V22" s="34" t="s">
         <v>196</v>
       </c>
       <c r="W22" s="15" t="s">
@@ -6304,7 +6339,7 @@
         <v>275091.90999999922</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="393.75" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>22</v>
       </c>
@@ -6326,7 +6361,7 @@
       <c r="G23" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H23" s="38" t="s">
+      <c r="H23" s="35" t="s">
         <v>200</v>
       </c>
       <c r="I23" s="10">
@@ -6336,7 +6371,7 @@
       <c r="J23" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="K23" s="33" t="s">
+      <c r="K23" s="31" t="s">
         <v>202</v>
       </c>
       <c r="L23" s="11" t="s">
@@ -6351,10 +6386,10 @@
       <c r="O23" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="P23" s="36">
+      <c r="P23" s="75">
         <v>14.5405</v>
       </c>
-      <c r="Q23" s="36">
+      <c r="Q23" s="75">
         <v>-91.672200000000004</v>
       </c>
       <c r="R23" s="14">
@@ -6394,7 +6429,7 @@
         <v>1119833.4800000004</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>23</v>
       </c>
@@ -6426,7 +6461,7 @@
       <c r="J24" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="K24" s="39" t="s">
+      <c r="K24" s="36" t="s">
         <v>208</v>
       </c>
       <c r="L24" s="11" t="s">
@@ -6441,10 +6476,10 @@
       <c r="O24" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="P24" s="13">
+      <c r="P24" s="73">
         <v>14.4884086</v>
       </c>
-      <c r="Q24" s="13">
+      <c r="Q24" s="73">
         <v>-92.160963100000004</v>
       </c>
       <c r="R24" s="14">
@@ -6485,7 +6520,7 @@
         <v>4745430.0200000033</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>24</v>
       </c>
@@ -6514,10 +6549,10 @@
         <f t="shared" si="3"/>
         <v>0.81577987967317678</v>
       </c>
-      <c r="J25" s="40" t="s">
+      <c r="J25" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="K25" s="40" t="s">
+      <c r="K25" s="37" t="s">
         <v>216</v>
       </c>
       <c r="L25" s="21" t="s">
@@ -6532,10 +6567,10 @@
       <c r="O25" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="P25" s="28">
+      <c r="P25" s="74">
         <v>14.806900000000001</v>
       </c>
-      <c r="Q25" s="28">
+      <c r="Q25" s="74">
         <v>-91.404799999999994</v>
       </c>
       <c r="R25" s="24">
@@ -6575,7 +6610,7 @@
         <v>1569349.7599999998</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="337.5" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>25</v>
       </c>
@@ -6604,10 +6639,10 @@
         <f t="shared" si="3"/>
         <v>0.94731551283677107</v>
       </c>
-      <c r="J26" s="40" t="s">
+      <c r="J26" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="K26" s="41" t="s">
+      <c r="K26" s="38" t="s">
         <v>222</v>
       </c>
       <c r="L26" s="21" t="s">
@@ -6622,10 +6657,10 @@
       <c r="O26" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="P26" s="28">
+      <c r="P26" s="74">
         <v>14.5936</v>
       </c>
-      <c r="Q26" s="28">
+      <c r="Q26" s="74">
         <v>-91.5291</v>
       </c>
       <c r="R26" s="24">
@@ -6653,7 +6688,7 @@
         <f>-1540454.58+1540446.69-40481.97+927302.06+2062095.92-2955898.7+1092849.69+975180.12</f>
         <v>2061039.23</v>
       </c>
-      <c r="Z26" s="42">
+      <c r="Z26" s="39">
         <f t="shared" si="7"/>
         <v>16851039.23</v>
       </c>
@@ -6665,7 +6700,7 @@
         <v>887788.36000000127</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="300" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>26</v>
       </c>
@@ -6697,7 +6732,7 @@
       <c r="J27" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="K27" s="41" t="s">
+      <c r="K27" s="38" t="s">
         <v>229</v>
       </c>
       <c r="L27" s="21" t="s">
@@ -6712,10 +6747,10 @@
       <c r="O27" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="P27" s="28">
+      <c r="P27" s="74">
         <v>14.3960162</v>
       </c>
-      <c r="Q27" s="28">
+      <c r="Q27" s="74">
         <v>-91.319659000000001</v>
       </c>
       <c r="R27" s="24">
@@ -6730,10 +6765,10 @@
       <c r="U27" s="23">
         <v>0</v>
       </c>
-      <c r="V27" s="43" t="s">
+      <c r="V27" s="40" t="s">
         <v>231</v>
       </c>
-      <c r="W27" s="43" t="s">
+      <c r="W27" s="40" t="s">
         <v>232</v>
       </c>
       <c r="X27" s="26">
@@ -6754,7 +6789,7 @@
         <v>7479358.4299999997</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="273" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>27</v>
       </c>
@@ -6786,7 +6821,7 @@
       <c r="J28" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="K28" s="39" t="s">
+      <c r="K28" s="36" t="s">
         <v>236</v>
       </c>
       <c r="L28" s="11" t="s">
@@ -6801,10 +6836,10 @@
       <c r="O28" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="P28" s="13">
+      <c r="P28" s="73">
         <v>14.9181534</v>
       </c>
-      <c r="Q28" s="13">
+      <c r="Q28" s="73">
         <v>-91.443099500000002</v>
       </c>
       <c r="R28" s="14">
@@ -6844,7 +6879,7 @@
         <v>19949688.600000001</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" ht="312" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>28</v>
       </c>
@@ -6891,10 +6926,10 @@
       <c r="O29" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="P29" s="13">
+      <c r="P29" s="73">
         <v>15.1075903</v>
       </c>
-      <c r="Q29" s="13">
+      <c r="Q29" s="73">
         <v>-89.366608099999993</v>
       </c>
       <c r="R29" s="14">
@@ -6933,7 +6968,7 @@
         <v>63366828.200000003</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" ht="273" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>29</v>
       </c>
@@ -6980,10 +7015,10 @@
       <c r="O30" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="P30" s="13">
+      <c r="P30" s="73">
         <v>14.5047222</v>
       </c>
-      <c r="Q30" s="13">
+      <c r="Q30" s="73">
         <v>-90.951111100000006</v>
       </c>
       <c r="R30" s="14">
@@ -6998,7 +7033,7 @@
       <c r="U30" s="12">
         <v>0</v>
       </c>
-      <c r="V30" s="44" t="s">
+      <c r="V30" s="41" t="s">
         <v>255</v>
       </c>
       <c r="W30" s="15" t="s">
@@ -7023,7 +7058,7 @@
         <v>4622768.07</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="390" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>30</v>
       </c>
@@ -7070,10 +7105,10 @@
       <c r="O31" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="P31" s="45">
+      <c r="P31" s="73">
         <v>14.3744917</v>
       </c>
-      <c r="Q31" s="31">
+      <c r="Q31" s="73">
         <v>-91.133122222222198</v>
       </c>
       <c r="R31" s="14">
@@ -7088,7 +7123,7 @@
       <c r="U31" s="12">
         <v>0</v>
       </c>
-      <c r="V31" s="46" t="s">
+      <c r="V31" s="42" t="s">
         <v>255</v>
       </c>
       <c r="W31" s="15" t="s">
@@ -7112,7 +7147,7 @@
         <v>10993403.82</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>31</v>
       </c>
@@ -7159,10 +7194,10 @@
       <c r="O32" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="P32" s="45">
+      <c r="P32" s="73">
         <v>14.8544444</v>
       </c>
-      <c r="Q32" s="31">
+      <c r="Q32" s="73">
         <v>-92.078611111111101</v>
       </c>
       <c r="R32" s="14">
@@ -7177,10 +7212,10 @@
       <c r="U32" s="12">
         <v>0</v>
       </c>
-      <c r="V32" s="47" t="s">
+      <c r="V32" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="W32" s="48" t="s">
+      <c r="W32" s="44" t="s">
         <v>269</v>
       </c>
       <c r="X32" s="18">
@@ -7202,7 +7237,7 @@
         <v>17300836.84</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>32</v>
       </c>
@@ -7215,16 +7250,16 @@
       <c r="D33" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E33" s="37" t="s">
+      <c r="E33" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="F33" s="37" t="s">
+      <c r="F33" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="G33" s="37" t="s">
+      <c r="G33" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="H33" s="38" t="s">
+      <c r="H33" s="35" t="s">
         <v>273</v>
       </c>
       <c r="I33" s="10">
@@ -7240,19 +7275,19 @@
       <c r="L33" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M33" s="49" t="s">
+      <c r="M33" s="45" t="s">
         <v>276</v>
       </c>
       <c r="N33" s="12">
         <v>16356292</v>
       </c>
-      <c r="O33" s="50" t="s">
+      <c r="O33" s="46" t="s">
         <v>277</v>
       </c>
-      <c r="P33" s="13">
+      <c r="P33" s="73">
         <v>15.337723199999999</v>
       </c>
-      <c r="Q33" s="13">
+      <c r="Q33" s="73">
         <v>-89.743525700000006</v>
       </c>
       <c r="R33" s="14">
@@ -7267,16 +7302,16 @@
       <c r="U33" s="12">
         <v>90</v>
       </c>
-      <c r="V33" s="51" t="s">
+      <c r="V33" s="47" t="s">
         <v>278</v>
       </c>
       <c r="W33" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="X33" s="52">
+      <c r="X33" s="48">
         <v>1854234.46</v>
       </c>
-      <c r="Y33" s="52">
+      <c r="Y33" s="48">
         <f>-831467.56+831466.56-884017.8+884014.3-34376.1+398311.14+151889.33-490961.42+403972.05</f>
         <v>428830.5</v>
       </c>
@@ -7292,7 +7327,7 @@
         <v>286716.45999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>33</v>
       </c>
@@ -7305,16 +7340,16 @@
       <c r="D34" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E34" s="37" t="s">
+      <c r="E34" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="F34" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="G34" s="37" t="s">
+      <c r="G34" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="38" t="s">
+      <c r="H34" s="35" t="s">
         <v>282</v>
       </c>
       <c r="I34" s="10">
@@ -7330,19 +7365,19 @@
       <c r="L34" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M34" s="49" t="s">
+      <c r="M34" s="45" t="s">
         <v>276</v>
       </c>
       <c r="N34" s="12">
         <v>16356292</v>
       </c>
-      <c r="O34" s="50" t="s">
+      <c r="O34" s="46" t="s">
         <v>277</v>
       </c>
-      <c r="P34" s="13">
+      <c r="P34" s="73">
         <v>15.392986199999999</v>
       </c>
-      <c r="Q34" s="13">
+      <c r="Q34" s="73">
         <v>-89.646835300000006</v>
       </c>
       <c r="R34" s="14">
@@ -7357,16 +7392,16 @@
       <c r="U34" s="12">
         <v>90</v>
       </c>
-      <c r="V34" s="51" t="s">
+      <c r="V34" s="47" t="s">
         <v>278</v>
       </c>
       <c r="W34" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="X34" s="52">
+      <c r="X34" s="48">
         <v>3122114.42</v>
       </c>
-      <c r="Y34" s="52">
+      <c r="Y34" s="48">
         <f>-986156.58+986159.06-48892.2+48890.87-986528.04+986529.36-989897.23+989882.05-197449.99+168657.15+507016.09-434400.63+522186.34</f>
         <v>565996.25000000023</v>
       </c>
@@ -7382,7 +7417,7 @@
         <v>904132.69</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>34</v>
       </c>
@@ -7395,44 +7430,44 @@
       <c r="D35" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E35" s="43" t="s">
+      <c r="E35" s="40" t="s">
         <v>283</v>
       </c>
-      <c r="F35" s="43" t="s">
+      <c r="F35" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="G35" s="43" t="s">
+      <c r="G35" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H35" s="53">
+      <c r="H35" s="49">
         <v>0.76</v>
       </c>
       <c r="I35" s="22">
         <f t="shared" si="3"/>
         <v>0.89998137157454505</v>
       </c>
-      <c r="J35" s="40" t="s">
+      <c r="J35" s="37" t="s">
         <v>285</v>
       </c>
-      <c r="K35" s="40" t="s">
+      <c r="K35" s="37" t="s">
         <v>286</v>
       </c>
       <c r="L35" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M35" s="43" t="s">
+      <c r="M35" s="40" t="s">
         <v>287</v>
       </c>
       <c r="N35" s="23">
         <v>16649710</v>
       </c>
-      <c r="O35" s="53" t="s">
+      <c r="O35" s="49" t="s">
         <v>288</v>
       </c>
-      <c r="P35" s="23">
+      <c r="P35" s="74">
         <v>15.369643699999999</v>
       </c>
-      <c r="Q35" s="23">
+      <c r="Q35" s="74">
         <v>-90.547197600000004</v>
       </c>
       <c r="R35" s="24">
@@ -7447,16 +7482,16 @@
       <c r="U35" s="23">
         <v>0</v>
       </c>
-      <c r="V35" s="53" t="s">
+      <c r="V35" s="49" t="s">
         <v>289</v>
       </c>
-      <c r="W35" s="53" t="s">
+      <c r="W35" s="49" t="s">
         <v>290</v>
       </c>
-      <c r="X35" s="54">
+      <c r="X35" s="50">
         <v>1106000</v>
       </c>
-      <c r="Y35" s="54">
+      <c r="Y35" s="50">
         <v>181441.07000000004</v>
       </c>
       <c r="Z35" s="26">
@@ -7471,7 +7506,7 @@
         <v>128768.09000000008</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="292.5" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>35</v>
       </c>
@@ -7484,16 +7519,16 @@
       <c r="D36" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E36" s="43" t="s">
+      <c r="E36" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="F36" s="43" t="s">
+      <c r="F36" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="G36" s="43" t="s">
+      <c r="G36" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H36" s="53">
+      <c r="H36" s="49">
         <v>0</v>
       </c>
       <c r="I36" s="22">
@@ -7509,19 +7544,19 @@
       <c r="L36" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M36" s="43" t="s">
+      <c r="M36" s="40" t="s">
         <v>295</v>
       </c>
       <c r="N36" s="23">
         <v>16650085</v>
       </c>
-      <c r="O36" s="53" t="s">
+      <c r="O36" s="49" t="s">
         <v>296</v>
       </c>
-      <c r="P36" s="23">
+      <c r="P36" s="74">
         <v>15.3737452</v>
       </c>
-      <c r="Q36" s="23">
+      <c r="Q36" s="74">
         <v>-90.143979799999997</v>
       </c>
       <c r="R36" s="24">
@@ -7536,16 +7571,16 @@
       <c r="U36" s="23">
         <v>90</v>
       </c>
-      <c r="V36" s="53" t="s">
+      <c r="V36" s="49" t="s">
         <v>289</v>
       </c>
-      <c r="W36" s="53" t="s">
+      <c r="W36" s="49" t="s">
         <v>290</v>
       </c>
-      <c r="X36" s="54">
+      <c r="X36" s="50">
         <v>1204000</v>
       </c>
-      <c r="Y36" s="54">
+      <c r="Y36" s="50">
         <v>0</v>
       </c>
       <c r="Z36" s="26">
@@ -7560,7 +7595,7 @@
         <v>192617.18000000005</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>36</v>
       </c>
@@ -7573,16 +7608,16 @@
       <c r="D37" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E37" s="43" t="s">
+      <c r="E37" s="40" t="s">
         <v>297</v>
       </c>
-      <c r="F37" s="43" t="s">
+      <c r="F37" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="G37" s="43" t="s">
+      <c r="G37" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H37" s="53">
+      <c r="H37" s="49">
         <v>0.64500000000000002</v>
       </c>
       <c r="I37" s="22">
@@ -7598,19 +7633,19 @@
       <c r="L37" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M37" s="43" t="s">
+      <c r="M37" s="40" t="s">
         <v>295</v>
       </c>
       <c r="N37" s="23">
         <v>16650085</v>
       </c>
-      <c r="O37" s="53" t="s">
+      <c r="O37" s="49" t="s">
         <v>296</v>
       </c>
-      <c r="P37" s="23">
+      <c r="P37" s="74">
         <v>15.4213445</v>
       </c>
-      <c r="Q37" s="23">
+      <c r="Q37" s="74">
         <v>-90.244411900000003</v>
       </c>
       <c r="R37" s="24">
@@ -7625,16 +7660,16 @@
       <c r="U37" s="23">
         <v>90</v>
       </c>
-      <c r="V37" s="53" t="s">
+      <c r="V37" s="49" t="s">
         <v>289</v>
       </c>
-      <c r="W37" s="53" t="s">
+      <c r="W37" s="49" t="s">
         <v>290</v>
       </c>
-      <c r="X37" s="55">
+      <c r="X37" s="51">
         <v>770000</v>
       </c>
-      <c r="Y37" s="55">
+      <c r="Y37" s="51">
         <v>329602.2</v>
       </c>
       <c r="Z37" s="26">
@@ -7649,7 +7684,7 @@
         <v>112170.23999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>37</v>
       </c>
@@ -7662,16 +7697,16 @@
       <c r="D38" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E38" s="43" t="s">
+      <c r="E38" s="40" t="s">
         <v>298</v>
       </c>
-      <c r="F38" s="43" t="s">
+      <c r="F38" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="G38" s="43" t="s">
+      <c r="G38" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="53">
+      <c r="H38" s="49">
         <v>0.43</v>
       </c>
       <c r="I38" s="22">
@@ -7687,19 +7722,19 @@
       <c r="L38" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M38" s="56" t="s">
+      <c r="M38" s="52" t="s">
         <v>301</v>
       </c>
-      <c r="N38" s="43">
+      <c r="N38" s="40">
         <v>19308981</v>
       </c>
-      <c r="O38" s="53" t="s">
+      <c r="O38" s="49" t="s">
         <v>302</v>
       </c>
-      <c r="P38" s="28">
+      <c r="P38" s="74">
         <v>15.4777</v>
       </c>
-      <c r="Q38" s="28">
+      <c r="Q38" s="74">
         <v>-90.371600000000001</v>
       </c>
       <c r="R38" s="24">
@@ -7714,16 +7749,16 @@
       <c r="U38" s="23">
         <v>0</v>
       </c>
-      <c r="V38" s="53" t="s">
+      <c r="V38" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="W38" s="53" t="s">
+      <c r="W38" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="X38" s="54">
+      <c r="X38" s="50">
         <v>2400110.56</v>
       </c>
-      <c r="Y38" s="54">
+      <c r="Y38" s="50">
         <v>0</v>
       </c>
       <c r="Z38" s="26">
@@ -7738,7 +7773,7 @@
         <v>475579.51</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>38</v>
       </c>
@@ -7751,16 +7786,16 @@
       <c r="D39" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E39" s="43" t="s">
+      <c r="E39" s="40" t="s">
         <v>305</v>
       </c>
-      <c r="F39" s="43" t="s">
+      <c r="F39" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="G39" s="43" t="s">
+      <c r="G39" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H39" s="53">
+      <c r="H39" s="49">
         <v>0.38300000000000001</v>
       </c>
       <c r="I39" s="22">
@@ -7776,19 +7811,19 @@
       <c r="L39" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M39" s="56" t="s">
+      <c r="M39" s="52" t="s">
         <v>301</v>
       </c>
-      <c r="N39" s="43">
+      <c r="N39" s="40">
         <v>19308981</v>
       </c>
-      <c r="O39" s="53" t="s">
+      <c r="O39" s="49" t="s">
         <v>302</v>
       </c>
-      <c r="P39" s="28">
+      <c r="P39" s="74">
         <v>15.4787</v>
       </c>
-      <c r="Q39" s="28">
+      <c r="Q39" s="74">
         <v>-90.376000000000005</v>
       </c>
       <c r="R39" s="24">
@@ -7803,16 +7838,16 @@
       <c r="U39" s="23">
         <v>0</v>
       </c>
-      <c r="V39" s="53" t="s">
+      <c r="V39" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="W39" s="53" t="s">
+      <c r="W39" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="X39" s="54">
+      <c r="X39" s="50">
         <v>1421491.8</v>
       </c>
-      <c r="Y39" s="54">
+      <c r="Y39" s="50">
         <v>0</v>
       </c>
       <c r="Z39" s="26">
@@ -7827,7 +7862,7 @@
         <v>219004.06000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>39</v>
       </c>
@@ -7840,16 +7875,16 @@
       <c r="D40" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E40" s="43" t="s">
+      <c r="E40" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="F40" s="43" t="s">
+      <c r="F40" s="40" t="s">
         <v>307</v>
       </c>
-      <c r="G40" s="43" t="s">
+      <c r="G40" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H40" s="53">
+      <c r="H40" s="49">
         <v>0.2361</v>
       </c>
       <c r="I40" s="22">
@@ -7865,19 +7900,19 @@
       <c r="L40" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="M40" s="43" t="s">
+      <c r="M40" s="40" t="s">
         <v>310</v>
       </c>
       <c r="N40" s="23">
         <v>19309406</v>
       </c>
-      <c r="O40" s="53" t="s">
+      <c r="O40" s="49" t="s">
         <v>311</v>
       </c>
-      <c r="P40" s="23">
+      <c r="P40" s="74">
         <v>15.9311019</v>
       </c>
-      <c r="Q40" s="23">
+      <c r="Q40" s="74">
         <v>-90.511684900000006</v>
       </c>
       <c r="R40" s="24">
@@ -7892,16 +7927,16 @@
       <c r="U40" s="23">
         <v>0</v>
       </c>
-      <c r="V40" s="53" t="s">
+      <c r="V40" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="W40" s="53" t="s">
+      <c r="W40" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="X40" s="54">
+      <c r="X40" s="50">
         <v>4724513.1900000004</v>
       </c>
-      <c r="Y40" s="54">
+      <c r="Y40" s="50">
         <v>0</v>
       </c>
       <c r="Z40" s="26">
@@ -7916,7 +7951,7 @@
         <v>1620458.5300000003</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>40</v>
       </c>
@@ -7929,16 +7964,16 @@
       <c r="D41" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E41" s="37" t="s">
+      <c r="E41" s="34" t="s">
         <v>312</v>
       </c>
-      <c r="F41" s="37" t="s">
+      <c r="F41" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="G41" s="37" t="s">
+      <c r="G41" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="H41" s="38">
+      <c r="H41" s="35">
         <v>1</v>
       </c>
       <c r="I41" s="10">
@@ -7954,19 +7989,19 @@
       <c r="L41" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M41" s="57" t="s">
+      <c r="M41" s="53" t="s">
         <v>316</v>
       </c>
       <c r="N41" s="12">
         <v>18490387</v>
       </c>
-      <c r="O41" s="37" t="s">
+      <c r="O41" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="P41" s="31">
+      <c r="P41" s="73">
         <v>14.976800000000001</v>
       </c>
-      <c r="Q41" s="31">
+      <c r="Q41" s="73">
         <v>-90.144300000000001</v>
       </c>
       <c r="R41" s="14">
@@ -7981,16 +8016,16 @@
       <c r="U41" s="12">
         <v>90</v>
       </c>
-      <c r="V41" s="58" t="s">
+      <c r="V41" s="54" t="s">
         <v>231</v>
       </c>
-      <c r="W41" s="58" t="s">
+      <c r="W41" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="X41" s="52">
+      <c r="X41" s="48">
         <v>1529828.48</v>
       </c>
-      <c r="Y41" s="52">
+      <c r="Y41" s="48">
         <f>-205840.5+112911.51+37142.82-76100.15+93975.13+10402.44</f>
         <v>-27508.75</v>
       </c>
@@ -8006,7 +8041,7 @@
         <v>213878.97999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>41</v>
       </c>
@@ -8019,16 +8054,16 @@
       <c r="D42" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E42" s="37" t="s">
+      <c r="E42" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="F42" s="37" t="s">
+      <c r="F42" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="G42" s="37" t="s">
+      <c r="G42" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="H42" s="38">
+      <c r="H42" s="35">
         <v>1</v>
       </c>
       <c r="I42" s="10">
@@ -8044,19 +8079,19 @@
       <c r="L42" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M42" s="57" t="s">
+      <c r="M42" s="53" t="s">
         <v>316</v>
       </c>
       <c r="N42" s="12">
         <v>18490387</v>
       </c>
-      <c r="O42" s="37" t="s">
+      <c r="O42" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="P42" s="31">
+      <c r="P42" s="73">
         <v>14.977499999999999</v>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q42" s="73">
         <v>-90.219099999999997</v>
       </c>
       <c r="R42" s="14">
@@ -8071,16 +8106,16 @@
       <c r="U42" s="12">
         <v>90</v>
       </c>
-      <c r="V42" s="58" t="s">
+      <c r="V42" s="54" t="s">
         <v>231</v>
       </c>
-      <c r="W42" s="58" t="s">
+      <c r="W42" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="X42" s="52">
+      <c r="X42" s="48">
         <v>475053.7</v>
       </c>
-      <c r="Y42" s="52">
+      <c r="Y42" s="48">
         <f>-125587+62137.25+446579.18-5625+52959.75+19238.85-130226.28+31498.2</f>
         <v>350974.95</v>
       </c>
@@ -8096,7 +8131,7 @@
         <v>46351.20000000007</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>42</v>
       </c>
@@ -8109,16 +8144,16 @@
       <c r="D43" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E43" s="37" t="s">
+      <c r="E43" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="F43" s="37" t="s">
+      <c r="F43" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="G43" s="37" t="s">
+      <c r="G43" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="H43" s="38">
+      <c r="H43" s="35">
         <v>1</v>
       </c>
       <c r="I43" s="10">
@@ -8134,19 +8169,19 @@
       <c r="L43" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M43" s="57" t="s">
+      <c r="M43" s="53" t="s">
         <v>316</v>
       </c>
       <c r="N43" s="12">
         <v>18490387</v>
       </c>
-      <c r="O43" s="37" t="s">
+      <c r="O43" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="P43" s="31">
+      <c r="P43" s="73">
         <v>14.919</v>
       </c>
-      <c r="Q43" s="31">
+      <c r="Q43" s="73">
         <v>-90.150999999999996</v>
       </c>
       <c r="R43" s="14">
@@ -8161,16 +8196,16 @@
       <c r="U43" s="12">
         <v>90</v>
       </c>
-      <c r="V43" s="58" t="s">
+      <c r="V43" s="54" t="s">
         <v>231</v>
       </c>
-      <c r="W43" s="58" t="s">
+      <c r="W43" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="X43" s="52">
+      <c r="X43" s="48">
         <v>782362.4</v>
       </c>
-      <c r="Y43" s="52">
+      <c r="Y43" s="48">
         <f>-41245+286730.4+5756.3-99105.1+46551.08+572</f>
         <v>199259.68</v>
       </c>
@@ -8186,7 +8221,7 @@
         <v>321858.9800000001</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>43</v>
       </c>
@@ -8199,16 +8234,16 @@
       <c r="D44" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E44" s="37" t="s">
+      <c r="E44" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="F44" s="37" t="s">
+      <c r="F44" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="G44" s="37" t="s">
+      <c r="G44" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="H44" s="38">
+      <c r="H44" s="35">
         <v>1</v>
       </c>
       <c r="I44" s="10">
@@ -8224,19 +8259,19 @@
       <c r="L44" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M44" s="57" t="s">
+      <c r="M44" s="53" t="s">
         <v>316</v>
       </c>
       <c r="N44" s="12">
         <v>18490387</v>
       </c>
-      <c r="O44" s="37" t="s">
+      <c r="O44" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="P44" s="13">
+      <c r="P44" s="73">
         <v>14.998562099999999</v>
       </c>
-      <c r="Q44" s="13">
+      <c r="Q44" s="73">
         <v>-90.078669000000005</v>
       </c>
       <c r="R44" s="14">
@@ -8251,16 +8286,16 @@
       <c r="U44" s="12">
         <v>90</v>
       </c>
-      <c r="V44" s="58" t="s">
+      <c r="V44" s="54" t="s">
         <v>231</v>
       </c>
-      <c r="W44" s="58" t="s">
+      <c r="W44" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="X44" s="52">
+      <c r="X44" s="48">
         <v>580654.42000000004</v>
       </c>
-      <c r="Y44" s="52">
+      <c r="Y44" s="48">
         <f>-44592.5+65730.96+6802.9-9705+53744.3</f>
         <v>71980.66</v>
       </c>
@@ -8276,7 +8311,7 @@
         <v>162239.7300000001</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>44</v>
       </c>
@@ -8289,16 +8324,16 @@
       <c r="D45" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E45" s="43" t="s">
+      <c r="E45" s="40" t="s">
         <v>323</v>
       </c>
-      <c r="F45" s="43" t="s">
+      <c r="F45" s="40" t="s">
         <v>324</v>
       </c>
-      <c r="G45" s="43" t="s">
+      <c r="G45" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="H45" s="53">
+      <c r="H45" s="49">
         <v>0.63780000000000003</v>
       </c>
       <c r="I45" s="22">
@@ -8314,19 +8349,19 @@
       <c r="L45" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="M45" s="43" t="s">
+      <c r="M45" s="40" t="s">
         <v>327</v>
       </c>
       <c r="N45" s="23">
         <v>19506597</v>
       </c>
-      <c r="O45" s="53" t="s">
+      <c r="O45" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="P45" s="23">
+      <c r="P45" s="74">
         <v>13.975298199999999</v>
       </c>
-      <c r="Q45" s="23">
+      <c r="Q45" s="74">
         <v>-90.964597299999994</v>
       </c>
       <c r="R45" s="24">
@@ -8341,16 +8376,16 @@
       <c r="U45" s="23">
         <v>0</v>
       </c>
-      <c r="V45" s="53" t="s">
+      <c r="V45" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="W45" s="43" t="s">
+      <c r="W45" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="X45" s="54">
+      <c r="X45" s="50">
         <v>3265726.3</v>
       </c>
-      <c r="Y45" s="54">
+      <c r="Y45" s="50">
         <v>963432.34</v>
       </c>
       <c r="Z45" s="26">
@@ -8365,7 +8400,7 @@
         <v>423524.07999999961</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>45</v>
       </c>
@@ -8378,16 +8413,16 @@
       <c r="D46" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E46" s="43" t="s">
+      <c r="E46" s="40" t="s">
         <v>331</v>
       </c>
-      <c r="F46" s="43" t="s">
+      <c r="F46" s="40" t="s">
         <v>332</v>
       </c>
-      <c r="G46" s="43" t="s">
+      <c r="G46" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="H46" s="53">
+      <c r="H46" s="49">
         <v>0.7681</v>
       </c>
       <c r="I46" s="22">
@@ -8403,19 +8438,19 @@
       <c r="L46" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="M46" s="43" t="s">
+      <c r="M46" s="40" t="s">
         <v>327</v>
       </c>
       <c r="N46" s="23">
         <v>19506597</v>
       </c>
-      <c r="O46" s="53" t="s">
+      <c r="O46" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="P46" s="28">
+      <c r="P46" s="74">
         <v>13.926399999999999</v>
       </c>
-      <c r="Q46" s="28">
+      <c r="Q46" s="74">
         <v>-90.8904</v>
       </c>
       <c r="R46" s="24">
@@ -8430,16 +8465,16 @@
       <c r="U46" s="23">
         <v>0</v>
       </c>
-      <c r="V46" s="53" t="s">
+      <c r="V46" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="W46" s="43" t="s">
+      <c r="W46" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="X46" s="54">
+      <c r="X46" s="50">
         <v>1873273.7</v>
       </c>
-      <c r="Y46" s="54">
+      <c r="Y46" s="50">
         <v>1092035.3600000001</v>
       </c>
       <c r="Z46" s="26">
@@ -8454,7 +8489,7 @@
         <v>297082.78000000026</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>46</v>
       </c>
@@ -8467,16 +8502,16 @@
       <c r="D47" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E47" s="43" t="s">
+      <c r="E47" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="F47" s="43" t="s">
+      <c r="F47" s="40" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="43" t="s">
+      <c r="G47" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="H47" s="53">
+      <c r="H47" s="49">
         <v>0.52769999999999995</v>
       </c>
       <c r="I47" s="22">
@@ -8492,19 +8527,19 @@
       <c r="L47" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="M47" s="56" t="s">
+      <c r="M47" s="52" t="s">
         <v>337</v>
       </c>
       <c r="N47" s="23">
         <v>19506686</v>
       </c>
-      <c r="O47" s="53" t="s">
+      <c r="O47" s="49" t="s">
         <v>338</v>
       </c>
-      <c r="P47" s="28">
+      <c r="P47" s="74">
         <v>13.9253</v>
       </c>
-      <c r="Q47" s="28">
+      <c r="Q47" s="74">
         <v>-90.822100000000006</v>
       </c>
       <c r="R47" s="24">
@@ -8519,16 +8554,16 @@
       <c r="U47" s="23">
         <v>240</v>
       </c>
-      <c r="V47" s="53" t="s">
+      <c r="V47" s="49" t="s">
         <v>204</v>
       </c>
-      <c r="W47" s="43" t="s">
+      <c r="W47" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="X47" s="54">
+      <c r="X47" s="50">
         <v>3698012.22</v>
       </c>
-      <c r="Y47" s="54">
+      <c r="Y47" s="50">
         <v>-2.0699999999999998</v>
       </c>
       <c r="Z47" s="26">
@@ -8543,7 +8578,7 @@
         <v>254457.16000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>47</v>
       </c>
@@ -8556,44 +8591,44 @@
       <c r="D48" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E48" s="43" t="s">
+      <c r="E48" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="F48" s="43" t="s">
+      <c r="F48" s="40" t="s">
         <v>332</v>
       </c>
-      <c r="G48" s="43" t="s">
+      <c r="G48" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="H48" s="53">
+      <c r="H48" s="49">
         <v>0.50490000000000002</v>
       </c>
       <c r="I48" s="22">
         <f t="shared" si="3"/>
         <v>0.84191913558457954</v>
       </c>
-      <c r="J48" s="40" t="s">
+      <c r="J48" s="37" t="s">
         <v>340</v>
       </c>
-      <c r="K48" s="40" t="s">
+      <c r="K48" s="37" t="s">
         <v>341</v>
       </c>
       <c r="L48" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="M48" s="56" t="s">
+      <c r="M48" s="52" t="s">
         <v>337</v>
       </c>
       <c r="N48" s="23">
         <v>19506686</v>
       </c>
-      <c r="O48" s="53" t="s">
+      <c r="O48" s="49" t="s">
         <v>338</v>
       </c>
-      <c r="P48" s="28">
+      <c r="P48" s="74">
         <v>13.917899999999999</v>
       </c>
-      <c r="Q48" s="28">
+      <c r="Q48" s="74">
         <v>-90.914699999999996</v>
       </c>
       <c r="R48" s="24">
@@ -8608,16 +8643,16 @@
       <c r="U48" s="23">
         <v>240</v>
       </c>
-      <c r="V48" s="53" t="s">
+      <c r="V48" s="49" t="s">
         <v>204</v>
       </c>
-      <c r="W48" s="43" t="s">
+      <c r="W48" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="X48" s="54">
+      <c r="X48" s="50">
         <v>1991987.78</v>
       </c>
-      <c r="Y48" s="54">
+      <c r="Y48" s="50">
         <v>-12.21</v>
       </c>
       <c r="Z48" s="26">
@@ -8632,7 +8667,7 @@
         <v>314893.21999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>48</v>
       </c>
@@ -8645,16 +8680,16 @@
       <c r="D49" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E49" s="37" t="s">
+      <c r="E49" s="34" t="s">
         <v>342</v>
       </c>
-      <c r="F49" s="37" t="s">
+      <c r="F49" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="G49" s="37" t="s">
+      <c r="G49" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H49" s="38">
+      <c r="H49" s="35">
         <v>1</v>
       </c>
       <c r="I49" s="10">
@@ -8663,25 +8698,25 @@
       <c r="J49" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="K49" s="59" t="s">
+      <c r="K49" s="55" t="s">
         <v>344</v>
       </c>
       <c r="L49" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="M49" s="49" t="s">
+      <c r="M49" s="45" t="s">
         <v>345</v>
       </c>
       <c r="N49" s="12">
         <v>13117203</v>
       </c>
-      <c r="O49" s="37" t="s">
+      <c r="O49" s="34" t="s">
         <v>346</v>
       </c>
-      <c r="P49" s="31">
+      <c r="P49" s="73">
         <v>14.6655</v>
       </c>
-      <c r="Q49" s="31">
+      <c r="Q49" s="73">
         <v>-90.491200000000006</v>
       </c>
       <c r="R49" s="14">
@@ -8696,16 +8731,16 @@
       <c r="U49" s="12">
         <v>100</v>
       </c>
-      <c r="V49" s="58" t="s">
+      <c r="V49" s="54" t="s">
         <v>347</v>
       </c>
-      <c r="W49" s="58" t="s">
+      <c r="W49" s="54" t="s">
         <v>348</v>
       </c>
-      <c r="X49" s="52">
+      <c r="X49" s="48">
         <v>1140000</v>
       </c>
-      <c r="Y49" s="52">
+      <c r="Y49" s="48">
         <v>364012.05000000005</v>
       </c>
       <c r="Z49" s="18">
@@ -8720,7 +8755,7 @@
         <v>150972.25</v>
       </c>
     </row>
-    <row r="50" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>49</v>
       </c>
@@ -8733,16 +8768,16 @@
       <c r="D50" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E50" s="37" t="s">
+      <c r="E50" s="34" t="s">
         <v>349</v>
       </c>
-      <c r="F50" s="37" t="s">
+      <c r="F50" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="G50" s="37" t="s">
+      <c r="G50" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H50" s="38">
+      <c r="H50" s="35">
         <v>1</v>
       </c>
       <c r="I50" s="10">
@@ -8751,23 +8786,23 @@
       <c r="J50" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="K50" s="60"/>
+      <c r="K50" s="56"/>
       <c r="L50" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="M50" s="49" t="s">
+      <c r="M50" s="45" t="s">
         <v>345</v>
       </c>
       <c r="N50" s="12">
         <v>13117203</v>
       </c>
-      <c r="O50" s="37" t="s">
+      <c r="O50" s="34" t="s">
         <v>346</v>
       </c>
-      <c r="P50" s="61">
+      <c r="P50" s="76">
         <v>14.658200000000001</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="73">
         <v>-90.49</v>
       </c>
       <c r="R50" s="14">
@@ -8782,16 +8817,16 @@
       <c r="U50" s="12">
         <v>100</v>
       </c>
-      <c r="V50" s="58" t="s">
+      <c r="V50" s="54" t="s">
         <v>347</v>
       </c>
-      <c r="W50" s="58" t="s">
+      <c r="W50" s="54" t="s">
         <v>348</v>
       </c>
-      <c r="X50" s="52">
+      <c r="X50" s="48">
         <v>4270000</v>
       </c>
-      <c r="Y50" s="52">
+      <c r="Y50" s="48">
         <v>715323.3</v>
       </c>
       <c r="Z50" s="18">
@@ -8806,7 +8841,7 @@
         <v>500268.9299999997</v>
       </c>
     </row>
-    <row r="51" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" ht="273" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>50</v>
       </c>
@@ -8819,16 +8854,16 @@
       <c r="D51" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E51" s="37" t="s">
+      <c r="E51" s="34" t="s">
         <v>350</v>
       </c>
-      <c r="F51" s="37" t="s">
+      <c r="F51" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="G51" s="37" t="s">
+      <c r="G51" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H51" s="38">
+      <c r="H51" s="35">
         <v>0.80430000000000001</v>
       </c>
       <c r="I51" s="10">
@@ -8837,25 +8872,25 @@
       <c r="J51" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="K51" s="59" t="s">
+      <c r="K51" s="55" t="s">
         <v>352</v>
       </c>
       <c r="L51" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="M51" s="57" t="s">
+      <c r="M51" s="53" t="s">
         <v>353</v>
       </c>
       <c r="N51" s="12">
         <v>19375662</v>
       </c>
-      <c r="O51" s="50" t="s">
+      <c r="O51" s="46" t="s">
         <v>354</v>
       </c>
-      <c r="P51" s="61">
+      <c r="P51" s="76">
         <v>14.6576</v>
       </c>
-      <c r="Q51" s="31">
+      <c r="Q51" s="73">
         <v>-90.469399999999993</v>
       </c>
       <c r="R51" s="14">
@@ -8870,16 +8905,16 @@
       <c r="U51" s="12">
         <v>0</v>
       </c>
-      <c r="V51" s="51" t="s">
+      <c r="V51" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="W51" s="58" t="s">
+      <c r="W51" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="X51" s="52">
+      <c r="X51" s="48">
         <v>1666176.51</v>
       </c>
-      <c r="Y51" s="52">
+      <c r="Y51" s="48">
         <v>0</v>
       </c>
       <c r="Z51" s="18">
@@ -8894,7 +8929,7 @@
         <v>190413.78000000003</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>51</v>
       </c>
@@ -8907,16 +8942,16 @@
       <c r="D52" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E52" s="37" t="s">
+      <c r="E52" s="34" t="s">
         <v>357</v>
       </c>
-      <c r="F52" s="37" t="s">
+      <c r="F52" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="G52" s="37" t="s">
+      <c r="G52" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H52" s="38">
+      <c r="H52" s="35">
         <v>0.89380000000000004</v>
       </c>
       <c r="I52" s="10">
@@ -8925,23 +8960,23 @@
       <c r="J52" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="K52" s="60"/>
+      <c r="K52" s="56"/>
       <c r="L52" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="M52" s="57" t="s">
+      <c r="M52" s="53" t="s">
         <v>353</v>
       </c>
       <c r="N52" s="12">
         <v>19375662</v>
       </c>
-      <c r="O52" s="50" t="s">
+      <c r="O52" s="46" t="s">
         <v>354</v>
       </c>
-      <c r="P52" s="31">
+      <c r="P52" s="73">
         <v>14.661099999999999</v>
       </c>
-      <c r="Q52" s="31">
+      <c r="Q52" s="73">
         <v>-90.445300000000003</v>
       </c>
       <c r="R52" s="14">
@@ -8956,16 +8991,16 @@
       <c r="U52" s="12">
         <v>0</v>
       </c>
-      <c r="V52" s="51" t="s">
+      <c r="V52" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="W52" s="58" t="s">
+      <c r="W52" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="X52" s="52">
+      <c r="X52" s="48">
         <v>4365253.49</v>
       </c>
-      <c r="Y52" s="52">
+      <c r="Y52" s="48">
         <v>0</v>
       </c>
       <c r="Z52" s="18">
@@ -8980,7 +9015,7 @@
         <v>1074768.2000000002</v>
       </c>
     </row>
-    <row r="53" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>52</v>
       </c>
@@ -8993,16 +9028,16 @@
       <c r="D53" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E53" s="43" t="s">
+      <c r="E53" s="40" t="s">
         <v>358</v>
       </c>
-      <c r="F53" s="43" t="s">
+      <c r="F53" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="G53" s="43" t="s">
+      <c r="G53" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H53" s="53">
+      <c r="H53" s="49">
         <v>0.60489999999999999</v>
       </c>
       <c r="I53" s="22">
@@ -9012,25 +9047,25 @@
       <c r="J53" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="K53" s="62" t="s">
+      <c r="K53" s="57" t="s">
         <v>360</v>
       </c>
       <c r="L53" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="M53" s="43" t="s">
+      <c r="M53" s="40" t="s">
         <v>287</v>
       </c>
       <c r="N53" s="23">
         <v>19446098</v>
       </c>
-      <c r="O53" s="53" t="s">
+      <c r="O53" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="P53" s="28">
+      <c r="P53" s="74">
         <v>14.651999999999999</v>
       </c>
-      <c r="Q53" s="28">
+      <c r="Q53" s="74">
         <v>-90.530299999999997</v>
       </c>
       <c r="R53" s="24">
@@ -9045,16 +9080,16 @@
       <c r="U53" s="23">
         <v>0</v>
       </c>
-      <c r="V53" s="53" t="s">
+      <c r="V53" s="49" t="s">
         <v>362</v>
       </c>
-      <c r="W53" s="43" t="s">
+      <c r="W53" s="40" t="s">
         <v>363</v>
       </c>
-      <c r="X53" s="54">
+      <c r="X53" s="50">
         <v>1439664.09</v>
       </c>
-      <c r="Y53" s="54">
+      <c r="Y53" s="50">
         <v>413079.42</v>
       </c>
       <c r="Z53" s="26">
@@ -9069,7 +9104,7 @@
         <v>186083.54000000004</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>53</v>
       </c>
@@ -9082,16 +9117,16 @@
       <c r="D54" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E54" s="43" t="s">
+      <c r="E54" s="40" t="s">
         <v>364</v>
       </c>
-      <c r="F54" s="43" t="s">
+      <c r="F54" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="G54" s="43" t="s">
+      <c r="G54" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H54" s="53">
+      <c r="H54" s="49">
         <v>0.48259999999999997</v>
       </c>
       <c r="I54" s="22">
@@ -9101,23 +9136,23 @@
       <c r="J54" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="K54" s="63"/>
+      <c r="K54" s="58"/>
       <c r="L54" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="M54" s="43" t="s">
+      <c r="M54" s="40" t="s">
         <v>287</v>
       </c>
       <c r="N54" s="23">
         <v>19446098</v>
       </c>
-      <c r="O54" s="53" t="s">
+      <c r="O54" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="P54" s="28">
+      <c r="P54" s="74">
         <v>14.6525</v>
       </c>
-      <c r="Q54" s="28">
+      <c r="Q54" s="74">
         <v>-90.530600000000007</v>
       </c>
       <c r="R54" s="24">
@@ -9132,16 +9167,16 @@
       <c r="U54" s="23">
         <v>0</v>
       </c>
-      <c r="V54" s="53" t="s">
+      <c r="V54" s="49" t="s">
         <v>362</v>
       </c>
-      <c r="W54" s="43" t="s">
+      <c r="W54" s="40" t="s">
         <v>363</v>
       </c>
-      <c r="X54" s="54">
+      <c r="X54" s="50">
         <v>2685335.91</v>
       </c>
-      <c r="Y54" s="54">
+      <c r="Y54" s="50">
         <v>409277.36</v>
       </c>
       <c r="Z54" s="26">
@@ -9156,7 +9191,7 @@
         <v>309942.04999999981</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>54</v>
       </c>
@@ -9169,16 +9204,16 @@
       <c r="D55" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="37" t="s">
+      <c r="E55" s="34" t="s">
         <v>365</v>
       </c>
-      <c r="F55" s="37" t="s">
+      <c r="F55" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="G55" s="37" t="s">
+      <c r="G55" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H55" s="38">
+      <c r="H55" s="35">
         <v>0.8478</v>
       </c>
       <c r="I55" s="10">
@@ -9187,25 +9222,25 @@
       <c r="J55" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="K55" s="59" t="s">
+      <c r="K55" s="55" t="s">
         <v>367</v>
       </c>
       <c r="L55" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="M55" s="57" t="s">
+      <c r="M55" s="53" t="s">
         <v>295</v>
       </c>
       <c r="N55" s="12">
         <v>19446330</v>
       </c>
-      <c r="O55" s="50" t="s">
+      <c r="O55" s="46" t="s">
         <v>368</v>
       </c>
-      <c r="P55" s="13">
+      <c r="P55" s="73">
         <v>14.6630775</v>
       </c>
-      <c r="Q55" s="13">
+      <c r="Q55" s="73">
         <v>-90.525619699999993</v>
       </c>
       <c r="R55" s="14">
@@ -9220,16 +9255,16 @@
       <c r="U55" s="13">
         <v>0</v>
       </c>
-      <c r="V55" s="51" t="s">
+      <c r="V55" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="W55" s="58" t="s">
+      <c r="W55" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="X55" s="52">
+      <c r="X55" s="48">
         <v>2946902.37</v>
       </c>
-      <c r="Y55" s="52">
+      <c r="Y55" s="48">
         <v>0</v>
       </c>
       <c r="Z55" s="18">
@@ -9244,7 +9279,7 @@
         <v>255724.70000000019</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>55</v>
       </c>
@@ -9257,16 +9292,16 @@
       <c r="D56" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E56" s="37" t="s">
+      <c r="E56" s="34" t="s">
         <v>369</v>
       </c>
-      <c r="F56" s="37" t="s">
+      <c r="F56" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="G56" s="37" t="s">
+      <c r="G56" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H56" s="38">
+      <c r="H56" s="35">
         <v>0.83850000000000002</v>
       </c>
       <c r="I56" s="10">
@@ -9275,23 +9310,23 @@
       <c r="J56" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="K56" s="60"/>
+      <c r="K56" s="56"/>
       <c r="L56" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="M56" s="57" t="s">
+      <c r="M56" s="53" t="s">
         <v>295</v>
       </c>
       <c r="N56" s="12">
         <v>19446330</v>
       </c>
-      <c r="O56" s="50" t="s">
+      <c r="O56" s="46" t="s">
         <v>368</v>
       </c>
-      <c r="P56" s="31">
+      <c r="P56" s="73">
         <v>14.647399999999999</v>
       </c>
-      <c r="Q56" s="31">
+      <c r="Q56" s="73">
         <v>-90.493899999999996</v>
       </c>
       <c r="R56" s="14">
@@ -9306,16 +9341,16 @@
       <c r="U56" s="13">
         <v>0</v>
       </c>
-      <c r="V56" s="51" t="s">
+      <c r="V56" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="W56" s="58" t="s">
+      <c r="W56" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="X56" s="52">
+      <c r="X56" s="48">
         <v>1718097.63</v>
       </c>
-      <c r="Y56" s="52">
+      <c r="Y56" s="48">
         <v>0</v>
       </c>
       <c r="Z56" s="18">
@@ -9330,7 +9365,7 @@
         <v>269745.93999999994</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" ht="273" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>56</v>
       </c>
@@ -9343,16 +9378,16 @@
       <c r="D57" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E57" s="37" t="s">
+      <c r="E57" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="F57" s="37" t="s">
+      <c r="F57" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="G57" s="37" t="s">
+      <c r="G57" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H57" s="38">
+      <c r="H57" s="35">
         <v>0.25</v>
       </c>
       <c r="I57" s="10">
@@ -9361,25 +9396,25 @@
       <c r="J57" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="K57" s="59" t="s">
+      <c r="K57" s="55" t="s">
         <v>372</v>
       </c>
       <c r="L57" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="M57" s="49" t="s">
+      <c r="M57" s="45" t="s">
         <v>373</v>
       </c>
       <c r="N57" s="12">
         <v>19446470</v>
       </c>
-      <c r="O57" s="50" t="s">
+      <c r="O57" s="46" t="s">
         <v>374</v>
       </c>
-      <c r="P57" s="13">
+      <c r="P57" s="73">
         <v>14.557048399999999</v>
       </c>
-      <c r="Q57" s="13">
+      <c r="Q57" s="73">
         <v>-90.619835699999996</v>
       </c>
       <c r="R57" s="14">
@@ -9394,16 +9429,16 @@
       <c r="U57" s="13">
         <v>0</v>
       </c>
-      <c r="V57" s="51" t="s">
+      <c r="V57" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="W57" s="58" t="s">
+      <c r="W57" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="X57" s="52">
+      <c r="X57" s="48">
         <v>907241.56</v>
       </c>
-      <c r="Y57" s="52">
+      <c r="Y57" s="48">
         <v>0</v>
       </c>
       <c r="Z57" s="18">
@@ -9418,7 +9453,7 @@
         <v>803711.56</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>57</v>
       </c>
@@ -9431,16 +9466,16 @@
       <c r="D58" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E58" s="37" t="s">
+      <c r="E58" s="34" t="s">
         <v>375</v>
       </c>
-      <c r="F58" s="37" t="s">
+      <c r="F58" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="G58" s="37" t="s">
+      <c r="G58" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H58" s="38">
+      <c r="H58" s="35">
         <v>0.52259999999999995</v>
       </c>
       <c r="I58" s="10">
@@ -9449,23 +9484,23 @@
       <c r="J58" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="K58" s="64"/>
+      <c r="K58" s="59"/>
       <c r="L58" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="M58" s="49" t="s">
+      <c r="M58" s="45" t="s">
         <v>373</v>
       </c>
       <c r="N58" s="12">
         <v>19446470</v>
       </c>
-      <c r="O58" s="50" t="s">
+      <c r="O58" s="46" t="s">
         <v>374</v>
       </c>
-      <c r="P58" s="13">
+      <c r="P58" s="73">
         <v>14.530029300000001</v>
       </c>
-      <c r="Q58" s="13">
+      <c r="Q58" s="73">
         <v>-90.620055399999998</v>
       </c>
       <c r="R58" s="14">
@@ -9480,16 +9515,16 @@
       <c r="U58" s="13">
         <v>0</v>
       </c>
-      <c r="V58" s="51" t="s">
+      <c r="V58" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="W58" s="58" t="s">
+      <c r="W58" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="X58" s="52">
+      <c r="X58" s="48">
         <v>3193968.56</v>
       </c>
-      <c r="Y58" s="52">
+      <c r="Y58" s="48">
         <v>0</v>
       </c>
       <c r="Z58" s="18">
@@ -9504,7 +9539,7 @@
         <v>2273779.56</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>58</v>
       </c>
@@ -9517,16 +9552,16 @@
       <c r="D59" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E59" s="37" t="s">
+      <c r="E59" s="34" t="s">
         <v>376</v>
       </c>
-      <c r="F59" s="37" t="s">
+      <c r="F59" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="G59" s="37" t="s">
+      <c r="G59" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H59" s="38">
+      <c r="H59" s="35">
         <v>0.7621</v>
       </c>
       <c r="I59" s="10">
@@ -9535,23 +9570,23 @@
       <c r="J59" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="K59" s="60"/>
+      <c r="K59" s="56"/>
       <c r="L59" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="M59" s="49" t="s">
+      <c r="M59" s="45" t="s">
         <v>373</v>
       </c>
       <c r="N59" s="12">
         <v>19446470</v>
       </c>
-      <c r="O59" s="50" t="s">
+      <c r="O59" s="46" t="s">
         <v>374</v>
       </c>
-      <c r="P59" s="13">
+      <c r="P59" s="73">
         <v>14.5546443</v>
       </c>
-      <c r="Q59" s="13">
+      <c r="Q59" s="73">
         <v>-90.566697899999994</v>
       </c>
       <c r="R59" s="14">
@@ -9566,16 +9601,16 @@
       <c r="U59" s="13">
         <v>0</v>
       </c>
-      <c r="V59" s="51" t="s">
+      <c r="V59" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="W59" s="58" t="s">
+      <c r="W59" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="X59" s="52">
+      <c r="X59" s="48">
         <v>2559589.88</v>
       </c>
-      <c r="Y59" s="52">
+      <c r="Y59" s="48">
         <v>0</v>
       </c>
       <c r="Z59" s="18">
@@ -9590,7 +9625,7 @@
         <v>1913745.38</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" ht="292.5" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>59</v>
       </c>
@@ -9603,16 +9638,16 @@
       <c r="D60" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E60" s="43" t="s">
+      <c r="E60" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="F60" s="43" t="s">
+      <c r="F60" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="G60" s="43" t="s">
+      <c r="G60" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H60" s="53">
+      <c r="H60" s="49">
         <v>0.74760000000000004</v>
       </c>
       <c r="I60" s="22">
@@ -9622,25 +9657,25 @@
       <c r="J60" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="K60" s="62" t="s">
+      <c r="K60" s="57" t="s">
         <v>380</v>
       </c>
       <c r="L60" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="M60" s="56" t="s">
+      <c r="M60" s="52" t="s">
         <v>381</v>
       </c>
       <c r="N60" s="23">
         <v>19446810</v>
       </c>
-      <c r="O60" s="53" t="s">
+      <c r="O60" s="49" t="s">
         <v>382</v>
       </c>
-      <c r="P60" s="28">
+      <c r="P60" s="74">
         <v>14.521800000000001</v>
       </c>
-      <c r="Q60" s="28">
+      <c r="Q60" s="74">
         <v>-90.5899</v>
       </c>
       <c r="R60" s="24">
@@ -9655,16 +9690,16 @@
       <c r="U60" s="23">
         <v>0</v>
       </c>
-      <c r="V60" s="53" t="s">
+      <c r="V60" s="49" t="s">
         <v>362</v>
       </c>
-      <c r="W60" s="43" t="s">
+      <c r="W60" s="40" t="s">
         <v>363</v>
       </c>
-      <c r="X60" s="54">
+      <c r="X60" s="50">
         <v>1964036.73</v>
       </c>
-      <c r="Y60" s="54">
+      <c r="Y60" s="50">
         <v>95127.79</v>
       </c>
       <c r="Z60" s="26">
@@ -9679,7 +9714,7 @@
         <v>212328.14000000013</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="370.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>60</v>
       </c>
@@ -9692,16 +9727,16 @@
       <c r="D61" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E61" s="43" t="s">
+      <c r="E61" s="40" t="s">
         <v>383</v>
       </c>
-      <c r="F61" s="43" t="s">
+      <c r="F61" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="G61" s="43" t="s">
+      <c r="G61" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H61" s="53">
+      <c r="H61" s="49">
         <v>0.65769999999999995</v>
       </c>
       <c r="I61" s="22">
@@ -9711,23 +9746,23 @@
       <c r="J61" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="K61" s="65"/>
+      <c r="K61" s="60"/>
       <c r="L61" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="M61" s="56" t="s">
+      <c r="M61" s="52" t="s">
         <v>381</v>
       </c>
       <c r="N61" s="23">
         <v>19446810</v>
       </c>
-      <c r="O61" s="53" t="s">
+      <c r="O61" s="49" t="s">
         <v>382</v>
       </c>
-      <c r="P61" s="28">
+      <c r="P61" s="74">
         <v>14.507</v>
       </c>
-      <c r="Q61" s="28">
+      <c r="Q61" s="74">
         <v>-90.595299999999995</v>
       </c>
       <c r="R61" s="24">
@@ -9742,16 +9777,16 @@
       <c r="U61" s="23">
         <v>0</v>
       </c>
-      <c r="V61" s="53" t="s">
+      <c r="V61" s="49" t="s">
         <v>362</v>
       </c>
-      <c r="W61" s="43" t="s">
+      <c r="W61" s="40" t="s">
         <v>363</v>
       </c>
-      <c r="X61" s="54">
+      <c r="X61" s="50">
         <v>2045013.39</v>
       </c>
-      <c r="Y61" s="54">
+      <c r="Y61" s="50">
         <v>935395.1</v>
       </c>
       <c r="Z61" s="26">
@@ -9766,7 +9801,7 @@
         <v>309036.30999999959</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" ht="351" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>61</v>
       </c>
@@ -9779,16 +9814,16 @@
       <c r="D62" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E62" s="43" t="s">
+      <c r="E62" s="40" t="s">
         <v>384</v>
       </c>
-      <c r="F62" s="43" t="s">
+      <c r="F62" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="G62" s="43" t="s">
+      <c r="G62" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H62" s="53">
+      <c r="H62" s="49">
         <v>0.39750000000000002</v>
       </c>
       <c r="I62" s="22">
@@ -9798,23 +9833,23 @@
       <c r="J62" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="K62" s="63"/>
+      <c r="K62" s="58"/>
       <c r="L62" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="M62" s="56" t="s">
+      <c r="M62" s="52" t="s">
         <v>381</v>
       </c>
       <c r="N62" s="23">
         <v>19446810</v>
       </c>
-      <c r="O62" s="53" t="s">
+      <c r="O62" s="49" t="s">
         <v>382</v>
       </c>
-      <c r="P62" s="23">
+      <c r="P62" s="74">
         <v>14.5688382</v>
       </c>
-      <c r="Q62" s="23">
+      <c r="Q62" s="74">
         <v>-90.599292599999998</v>
       </c>
       <c r="R62" s="24">
@@ -9829,16 +9864,16 @@
       <c r="U62" s="23">
         <v>0</v>
       </c>
-      <c r="V62" s="53" t="s">
+      <c r="V62" s="49" t="s">
         <v>362</v>
       </c>
-      <c r="W62" s="43" t="s">
+      <c r="W62" s="40" t="s">
         <v>363</v>
       </c>
-      <c r="X62" s="54">
+      <c r="X62" s="50">
         <v>977649.88</v>
       </c>
-      <c r="Y62" s="54">
+      <c r="Y62" s="50">
         <v>-44005</v>
       </c>
       <c r="Z62" s="26">
@@ -9853,7 +9888,7 @@
         <v>133599.77000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" ht="292.5" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>62</v>
       </c>
@@ -9866,16 +9901,16 @@
       <c r="D63" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E63" s="43" t="s">
+      <c r="E63" s="40" t="s">
         <v>385</v>
       </c>
-      <c r="F63" s="43" t="s">
+      <c r="F63" s="40" t="s">
         <v>386</v>
       </c>
-      <c r="G63" s="43" t="s">
+      <c r="G63" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H63" s="53">
+      <c r="H63" s="49">
         <v>0.1555</v>
       </c>
       <c r="I63" s="22">
@@ -9885,25 +9920,25 @@
       <c r="J63" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="K63" s="62" t="s">
+      <c r="K63" s="57" t="s">
         <v>388</v>
       </c>
       <c r="L63" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="M63" s="43" t="s">
+      <c r="M63" s="40" t="s">
         <v>389</v>
       </c>
       <c r="N63" s="23">
         <v>19446861</v>
       </c>
-      <c r="O63" s="53" t="s">
+      <c r="O63" s="49" t="s">
         <v>390</v>
       </c>
-      <c r="P63" s="28">
+      <c r="P63" s="74">
         <v>14.465199999999999</v>
       </c>
-      <c r="Q63" s="28">
+      <c r="Q63" s="74">
         <v>-90.531000000000006</v>
       </c>
       <c r="R63" s="24">
@@ -9918,22 +9953,22 @@
       <c r="U63" s="23">
         <v>0</v>
       </c>
-      <c r="V63" s="53" t="s">
+      <c r="V63" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="W63" s="43" t="s">
+      <c r="W63" s="40" t="s">
         <v>392</v>
       </c>
-      <c r="X63" s="54">
+      <c r="X63" s="50">
         <v>1150810.29</v>
       </c>
-      <c r="Y63" s="54">
-        <v>0</v>
-      </c>
-      <c r="Z63" s="54">
+      <c r="Y63" s="50">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="50">
         <v>1150810.29</v>
       </c>
-      <c r="AA63" s="54">
+      <c r="AA63" s="50">
         <v>0</v>
       </c>
       <c r="AB63" s="27">
@@ -9941,7 +9976,7 @@
         <v>1150810.29</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>63</v>
       </c>
@@ -9954,16 +9989,16 @@
       <c r="D64" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E64" s="43" t="s">
+      <c r="E64" s="40" t="s">
         <v>393</v>
       </c>
-      <c r="F64" s="43" t="s">
+      <c r="F64" s="40" t="s">
         <v>386</v>
       </c>
-      <c r="G64" s="43" t="s">
+      <c r="G64" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H64" s="53">
+      <c r="H64" s="49">
         <v>0</v>
       </c>
       <c r="I64" s="22">
@@ -9973,23 +10008,23 @@
       <c r="J64" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="K64" s="65"/>
+      <c r="K64" s="60"/>
       <c r="L64" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="M64" s="43" t="s">
+      <c r="M64" s="40" t="s">
         <v>389</v>
       </c>
       <c r="N64" s="23">
         <v>19446861</v>
       </c>
-      <c r="O64" s="53" t="s">
+      <c r="O64" s="49" t="s">
         <v>390</v>
       </c>
-      <c r="P64" s="28">
+      <c r="P64" s="74">
         <v>14.2781</v>
       </c>
-      <c r="Q64" s="28">
+      <c r="Q64" s="74">
         <v>-90.583699999999993</v>
       </c>
       <c r="R64" s="24">
@@ -10004,22 +10039,22 @@
       <c r="U64" s="23">
         <v>0</v>
       </c>
-      <c r="V64" s="53" t="s">
+      <c r="V64" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="W64" s="43" t="s">
+      <c r="W64" s="40" t="s">
         <v>392</v>
       </c>
-      <c r="X64" s="54">
+      <c r="X64" s="50">
         <v>1444153.53</v>
       </c>
-      <c r="Y64" s="54">
-        <v>0</v>
-      </c>
-      <c r="Z64" s="54">
+      <c r="Y64" s="50">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="50">
         <v>1444153.53</v>
       </c>
-      <c r="AA64" s="54">
+      <c r="AA64" s="50">
         <v>0</v>
       </c>
       <c r="AB64" s="27">
@@ -10027,7 +10062,7 @@
         <v>1444153.53</v>
       </c>
     </row>
-    <row r="65" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>64</v>
       </c>
@@ -10040,16 +10075,16 @@
       <c r="D65" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E65" s="43" t="s">
+      <c r="E65" s="40" t="s">
         <v>394</v>
       </c>
-      <c r="F65" s="43" t="s">
+      <c r="F65" s="40" t="s">
         <v>386</v>
       </c>
-      <c r="G65" s="43" t="s">
+      <c r="G65" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H65" s="53">
+      <c r="H65" s="49">
         <v>0</v>
       </c>
       <c r="I65" s="22">
@@ -10059,23 +10094,23 @@
       <c r="J65" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="K65" s="63"/>
+      <c r="K65" s="58"/>
       <c r="L65" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="M65" s="43" t="s">
+      <c r="M65" s="40" t="s">
         <v>389</v>
       </c>
       <c r="N65" s="23">
         <v>19446861</v>
       </c>
-      <c r="O65" s="53" t="s">
+      <c r="O65" s="49" t="s">
         <v>390</v>
       </c>
-      <c r="P65" s="28">
+      <c r="P65" s="74">
         <v>14.417899999999999</v>
       </c>
-      <c r="Q65" s="28">
+      <c r="Q65" s="74">
         <v>-90.494299999999996</v>
       </c>
       <c r="R65" s="24">
@@ -10090,22 +10125,22 @@
       <c r="U65" s="23">
         <v>0</v>
       </c>
-      <c r="V65" s="53" t="s">
+      <c r="V65" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="W65" s="43" t="s">
+      <c r="W65" s="40" t="s">
         <v>392</v>
       </c>
-      <c r="X65" s="54">
+      <c r="X65" s="50">
         <v>1077840.96</v>
       </c>
-      <c r="Y65" s="54">
-        <v>0</v>
-      </c>
-      <c r="Z65" s="54">
+      <c r="Y65" s="50">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="50">
         <v>1077840.96</v>
       </c>
-      <c r="AA65" s="54">
+      <c r="AA65" s="50">
         <v>0</v>
       </c>
       <c r="AB65" s="27">
@@ -10113,7 +10148,7 @@
         <v>1077840.96</v>
       </c>
     </row>
-    <row r="66" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" ht="312" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>65</v>
       </c>
@@ -10126,16 +10161,16 @@
       <c r="D66" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E66" s="43" t="s">
+      <c r="E66" s="40" t="s">
         <v>395</v>
       </c>
-      <c r="F66" s="43" t="s">
+      <c r="F66" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="G66" s="43" t="s">
+      <c r="G66" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H66" s="53">
+      <c r="H66" s="49">
         <v>0</v>
       </c>
       <c r="I66" s="22">
@@ -10151,19 +10186,19 @@
       <c r="L66" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="M66" s="43" t="s">
+      <c r="M66" s="40" t="s">
         <v>398</v>
       </c>
       <c r="N66" s="23">
         <v>20310013</v>
       </c>
-      <c r="O66" s="43" t="s">
+      <c r="O66" s="40" t="s">
         <v>399</v>
       </c>
-      <c r="P66" s="28">
+      <c r="P66" s="74">
         <v>14.647779999999999</v>
       </c>
-      <c r="Q66" s="28">
+      <c r="Q66" s="74">
         <v>-90.536342200000007</v>
       </c>
       <c r="R66" s="24">
@@ -10178,22 +10213,22 @@
       <c r="U66" s="23">
         <v>0</v>
       </c>
-      <c r="V66" s="43" t="s">
+      <c r="V66" s="40" t="s">
         <v>210</v>
       </c>
       <c r="W66" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="X66" s="55">
+      <c r="X66" s="51">
         <v>7549022.5999999996</v>
       </c>
-      <c r="Y66" s="55">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="55">
+      <c r="Y66" s="51">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="51">
         <v>7549022.5999999996</v>
       </c>
-      <c r="AA66" s="55">
+      <c r="AA66" s="51">
         <v>0</v>
       </c>
       <c r="AB66" s="27">
@@ -10201,7 +10236,7 @@
         <v>7549022.5999999996</v>
       </c>
     </row>
-    <row r="67" spans="1:28" ht="292.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>66</v>
       </c>
@@ -10214,16 +10249,16 @@
       <c r="D67" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E67" s="43" t="s">
+      <c r="E67" s="40" t="s">
         <v>400</v>
       </c>
-      <c r="F67" s="43" t="s">
+      <c r="F67" s="40" t="s">
         <v>401</v>
       </c>
-      <c r="G67" s="43" t="s">
+      <c r="G67" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="H67" s="53">
+      <c r="H67" s="49">
         <v>0.79769999999999996</v>
       </c>
       <c r="I67" s="22">
@@ -10233,25 +10268,25 @@
       <c r="J67" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="K67" s="62" t="s">
+      <c r="K67" s="57" t="s">
         <v>403</v>
       </c>
       <c r="L67" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="M67" s="43" t="s">
+      <c r="M67" s="40" t="s">
         <v>404</v>
       </c>
       <c r="N67" s="23">
         <v>18490565</v>
       </c>
-      <c r="O67" s="43" t="s">
+      <c r="O67" s="40" t="s">
         <v>405</v>
       </c>
-      <c r="P67" s="23">
+      <c r="P67" s="74">
         <v>15.607994700000001</v>
       </c>
-      <c r="Q67" s="23">
+      <c r="Q67" s="74">
         <v>-91.440571399999996</v>
       </c>
       <c r="R67" s="24">
@@ -10266,19 +10301,19 @@
       <c r="U67" s="23">
         <v>90</v>
       </c>
-      <c r="V67" s="43" t="s">
+      <c r="V67" s="40" t="s">
         <v>406</v>
       </c>
       <c r="W67" s="25" t="s">
         <v>407</v>
       </c>
-      <c r="X67" s="54">
+      <c r="X67" s="50">
         <v>1592687.03</v>
       </c>
-      <c r="Y67" s="54">
+      <c r="Y67" s="50">
         <v>277852.84000000003</v>
       </c>
-      <c r="Z67" s="42">
+      <c r="Z67" s="39">
         <f t="shared" ref="Z67:Z87" si="9">+X67+Y67</f>
         <v>1870539.87</v>
       </c>
@@ -10290,7 +10325,7 @@
         <v>180000.12000000011</v>
       </c>
     </row>
-    <row r="68" spans="1:28" ht="351" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" ht="273" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>67</v>
       </c>
@@ -10303,16 +10338,16 @@
       <c r="D68" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E68" s="43" t="s">
+      <c r="E68" s="40" t="s">
         <v>408</v>
       </c>
-      <c r="F68" s="43" t="s">
+      <c r="F68" s="40" t="s">
         <v>401</v>
       </c>
-      <c r="G68" s="43" t="s">
+      <c r="G68" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="H68" s="53">
+      <c r="H68" s="49">
         <v>0.89219999999999999</v>
       </c>
       <c r="I68" s="22">
@@ -10322,23 +10357,23 @@
       <c r="J68" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="K68" s="65"/>
+      <c r="K68" s="60"/>
       <c r="L68" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="M68" s="43" t="s">
+      <c r="M68" s="40" t="s">
         <v>404</v>
       </c>
       <c r="N68" s="23">
         <v>18490565</v>
       </c>
-      <c r="O68" s="43" t="s">
+      <c r="O68" s="40" t="s">
         <v>405</v>
       </c>
-      <c r="P68" s="28">
+      <c r="P68" s="74">
         <v>15.5539843</v>
       </c>
-      <c r="Q68" s="28">
+      <c r="Q68" s="74">
         <v>-91.437876000000003</v>
       </c>
       <c r="R68" s="24">
@@ -10353,19 +10388,19 @@
       <c r="U68" s="23">
         <v>90</v>
       </c>
-      <c r="V68" s="43" t="s">
+      <c r="V68" s="40" t="s">
         <v>406</v>
       </c>
       <c r="W68" s="25" t="s">
         <v>407</v>
       </c>
-      <c r="X68" s="54">
+      <c r="X68" s="50">
         <v>295572.09999999998</v>
       </c>
-      <c r="Y68" s="54">
+      <c r="Y68" s="50">
         <v>294284.99</v>
       </c>
-      <c r="Z68" s="42">
+      <c r="Z68" s="39">
         <f t="shared" si="9"/>
         <v>589857.09</v>
       </c>
@@ -10377,7 +10412,7 @@
         <v>21226.75</v>
       </c>
     </row>
-    <row r="69" spans="1:28" ht="292.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>68</v>
       </c>
@@ -10390,16 +10425,16 @@
       <c r="D69" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E69" s="43" t="s">
+      <c r="E69" s="40" t="s">
         <v>409</v>
       </c>
-      <c r="F69" s="43" t="s">
+      <c r="F69" s="40" t="s">
         <v>410</v>
       </c>
-      <c r="G69" s="43" t="s">
+      <c r="G69" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="H69" s="53">
+      <c r="H69" s="49">
         <v>0.75049999999999994</v>
       </c>
       <c r="I69" s="22">
@@ -10409,23 +10444,23 @@
       <c r="J69" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="K69" s="63"/>
+      <c r="K69" s="58"/>
       <c r="L69" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="M69" s="43" t="s">
+      <c r="M69" s="40" t="s">
         <v>404</v>
       </c>
       <c r="N69" s="23">
         <v>18490565</v>
       </c>
-      <c r="O69" s="43" t="s">
+      <c r="O69" s="40" t="s">
         <v>405</v>
       </c>
-      <c r="P69" s="23">
+      <c r="P69" s="74">
         <v>15.828105799999999</v>
       </c>
-      <c r="Q69" s="23">
+      <c r="Q69" s="74">
         <v>-91.478391999999999</v>
       </c>
       <c r="R69" s="24">
@@ -10440,19 +10475,19 @@
       <c r="U69" s="23">
         <v>90</v>
       </c>
-      <c r="V69" s="43" t="s">
+      <c r="V69" s="40" t="s">
         <v>406</v>
       </c>
       <c r="W69" s="25" t="s">
         <v>407</v>
       </c>
-      <c r="X69" s="54">
+      <c r="X69" s="50">
         <v>1360154.52</v>
       </c>
-      <c r="Y69" s="54">
+      <c r="Y69" s="50">
         <v>645778.87</v>
       </c>
-      <c r="Z69" s="42">
+      <c r="Z69" s="39">
         <f t="shared" si="9"/>
         <v>2005933.3900000001</v>
       </c>
@@ -10464,7 +10499,7 @@
         <v>245409.49000000022</v>
       </c>
     </row>
-    <row r="70" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>69</v>
       </c>
@@ -10477,16 +10512,16 @@
       <c r="D70" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E70" s="43" t="s">
+      <c r="E70" s="40" t="s">
         <v>411</v>
       </c>
-      <c r="F70" s="43" t="s">
+      <c r="F70" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="G70" s="43" t="s">
+      <c r="G70" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="H70" s="53">
+      <c r="H70" s="49">
         <v>0.57999999999999996</v>
       </c>
       <c r="I70" s="22">
@@ -10496,25 +10531,25 @@
       <c r="J70" s="21" t="s">
         <v>413</v>
       </c>
-      <c r="K70" s="62" t="s">
+      <c r="K70" s="57" t="s">
         <v>414</v>
       </c>
       <c r="L70" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="M70" s="56" t="s">
+      <c r="M70" s="52" t="s">
         <v>389</v>
       </c>
       <c r="N70" s="23">
         <v>17704928</v>
       </c>
-      <c r="O70" s="43" t="s">
+      <c r="O70" s="40" t="s">
         <v>415</v>
       </c>
-      <c r="P70" s="23">
+      <c r="P70" s="74">
         <v>14.5829298</v>
       </c>
-      <c r="Q70" s="23">
+      <c r="Q70" s="74">
         <v>-90.0962581</v>
       </c>
       <c r="R70" s="24">
@@ -10529,16 +10564,16 @@
       <c r="U70" s="23">
         <v>30</v>
       </c>
-      <c r="V70" s="43" t="s">
+      <c r="V70" s="40" t="s">
         <v>416</v>
       </c>
-      <c r="W70" s="43" t="s">
+      <c r="W70" s="40" t="s">
         <v>417</v>
       </c>
-      <c r="X70" s="54">
+      <c r="X70" s="50">
         <v>914244.44</v>
       </c>
-      <c r="Y70" s="54">
+      <c r="Y70" s="50">
         <v>-47645.849999999991</v>
       </c>
       <c r="Z70" s="26">
@@ -10553,7 +10588,7 @@
         <v>99636.010000000009</v>
       </c>
     </row>
-    <row r="71" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>70</v>
       </c>
@@ -10566,16 +10601,16 @@
       <c r="D71" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E71" s="43" t="s">
+      <c r="E71" s="40" t="s">
         <v>418</v>
       </c>
-      <c r="F71" s="43" t="s">
+      <c r="F71" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="G71" s="43" t="s">
+      <c r="G71" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="H71" s="53">
+      <c r="H71" s="49">
         <v>0.55000000000000004</v>
       </c>
       <c r="I71" s="22">
@@ -10585,23 +10620,23 @@
       <c r="J71" s="21" t="s">
         <v>413</v>
       </c>
-      <c r="K71" s="63"/>
+      <c r="K71" s="58"/>
       <c r="L71" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="M71" s="56" t="s">
+      <c r="M71" s="52" t="s">
         <v>389</v>
       </c>
       <c r="N71" s="23">
         <v>17704928</v>
       </c>
-      <c r="O71" s="43" t="s">
+      <c r="O71" s="40" t="s">
         <v>415</v>
       </c>
-      <c r="P71" s="23">
+      <c r="P71" s="74">
         <v>14.601954900000001</v>
       </c>
-      <c r="Q71" s="23">
+      <c r="Q71" s="74">
         <v>-90.057516100000001</v>
       </c>
       <c r="R71" s="24">
@@ -10616,16 +10651,16 @@
       <c r="U71" s="23">
         <v>30</v>
       </c>
-      <c r="V71" s="43" t="s">
+      <c r="V71" s="40" t="s">
         <v>416</v>
       </c>
-      <c r="W71" s="43" t="s">
+      <c r="W71" s="40" t="s">
         <v>417</v>
       </c>
-      <c r="X71" s="54">
+      <c r="X71" s="50">
         <v>914244.42</v>
       </c>
-      <c r="Y71" s="54">
+      <c r="Y71" s="50">
         <v>27659.110000000015</v>
       </c>
       <c r="Z71" s="26">
@@ -10640,7 +10675,7 @@
         <v>131346.28000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>71</v>
       </c>
@@ -10653,16 +10688,16 @@
       <c r="D72" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E72" s="37" t="s">
+      <c r="E72" s="34" t="s">
         <v>419</v>
       </c>
-      <c r="F72" s="37" t="s">
+      <c r="F72" s="34" t="s">
         <v>420</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="H72" s="38">
+      <c r="H72" s="35">
         <v>0.99</v>
       </c>
       <c r="I72" s="10">
@@ -10671,28 +10706,28 @@
       <c r="J72" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="K72" s="59" t="s">
+      <c r="K72" s="55" t="s">
         <v>422</v>
       </c>
       <c r="L72" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="M72" s="37" t="s">
+      <c r="M72" s="34" t="s">
         <v>316</v>
       </c>
       <c r="N72" s="12">
         <v>16129415</v>
       </c>
-      <c r="O72" s="50" t="s">
+      <c r="O72" s="46" t="s">
         <v>423</v>
       </c>
-      <c r="P72" s="36">
+      <c r="P72" s="75">
         <v>16.515260699999999</v>
       </c>
-      <c r="Q72" s="36">
+      <c r="Q72" s="75">
         <v>-90.199143000000007</v>
       </c>
-      <c r="R72" s="66">
+      <c r="R72" s="61">
         <v>44949</v>
       </c>
       <c r="S72" s="14">
@@ -10704,16 +10739,16 @@
       <c r="U72" s="12">
         <v>90</v>
       </c>
-      <c r="V72" s="51" t="s">
+      <c r="V72" s="47" t="s">
         <v>424</v>
       </c>
-      <c r="W72" s="51" t="s">
+      <c r="W72" s="47" t="s">
         <v>425</v>
       </c>
-      <c r="X72" s="52">
+      <c r="X72" s="48">
         <v>1617913.8</v>
       </c>
-      <c r="Y72" s="52">
+      <c r="Y72" s="48">
         <f>133686.89-167721.57+355426.64</f>
         <v>321391.96000000002</v>
       </c>
@@ -10729,7 +10764,7 @@
         <v>362865.38000000012</v>
       </c>
     </row>
-    <row r="73" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" ht="117" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>72</v>
       </c>
@@ -10742,16 +10777,16 @@
       <c r="D73" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E73" s="37" t="s">
+      <c r="E73" s="34" t="s">
         <v>426</v>
       </c>
-      <c r="F73" s="37" t="s">
+      <c r="F73" s="34" t="s">
         <v>420</v>
       </c>
       <c r="G73" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="H73" s="38">
+      <c r="H73" s="35">
         <v>0.99</v>
       </c>
       <c r="I73" s="10">
@@ -10760,23 +10795,23 @@
       <c r="J73" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="K73" s="60"/>
+      <c r="K73" s="56"/>
       <c r="L73" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="M73" s="37" t="s">
+      <c r="M73" s="34" t="s">
         <v>316</v>
       </c>
       <c r="N73" s="12">
         <v>16129415</v>
       </c>
-      <c r="O73" s="50" t="s">
+      <c r="O73" s="46" t="s">
         <v>423</v>
       </c>
-      <c r="P73" s="36">
+      <c r="P73" s="75">
         <v>16.519500000000001</v>
       </c>
-      <c r="Q73" s="36">
+      <c r="Q73" s="75">
         <v>-90.204499999999996</v>
       </c>
       <c r="R73" s="14">
@@ -10791,16 +10826,16 @@
       <c r="U73" s="12">
         <v>90</v>
       </c>
-      <c r="V73" s="51" t="s">
+      <c r="V73" s="47" t="s">
         <v>424</v>
       </c>
-      <c r="W73" s="51" t="s">
+      <c r="W73" s="47" t="s">
         <v>425</v>
       </c>
-      <c r="X73" s="52">
+      <c r="X73" s="48">
         <v>3690957.2</v>
       </c>
-      <c r="Y73" s="52">
+      <c r="Y73" s="48">
         <f>-951808.31+951805.93-567501.16+567500.99-946081.94+946085.42-840804.11+840743.38-642763.79+117899.93+444107.1+981966.19-539177.92+377800.81</f>
         <v>739772.52</v>
       </c>
@@ -10816,7 +10851,7 @@
         <v>1581299.5300000007</v>
       </c>
     </row>
-    <row r="74" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" ht="117" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>73</v>
       </c>
@@ -10829,16 +10864,16 @@
       <c r="D74" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E74" s="43" t="s">
+      <c r="E74" s="40" t="s">
         <v>427</v>
       </c>
-      <c r="F74" s="43" t="s">
+      <c r="F74" s="40" t="s">
         <v>428</v>
       </c>
       <c r="G74" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H74" s="53">
+      <c r="H74" s="49">
         <v>0.39710000000000001</v>
       </c>
       <c r="I74" s="22">
@@ -10848,25 +10883,25 @@
       <c r="J74" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="K74" s="62" t="s">
+      <c r="K74" s="57" t="s">
         <v>430</v>
       </c>
       <c r="L74" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="M74" s="43" t="s">
+      <c r="M74" s="40" t="s">
         <v>431</v>
       </c>
       <c r="N74" s="23">
         <v>13787322</v>
       </c>
-      <c r="O74" s="43" t="s">
+      <c r="O74" s="40" t="s">
         <v>432</v>
       </c>
-      <c r="P74" s="28">
+      <c r="P74" s="74">
         <v>15.356400000000001</v>
       </c>
-      <c r="Q74" s="28">
+      <c r="Q74" s="74">
         <v>-90.741</v>
       </c>
       <c r="R74" s="24">
@@ -10881,16 +10916,16 @@
       <c r="U74" s="23">
         <v>75</v>
       </c>
-      <c r="V74" s="43" t="s">
+      <c r="V74" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="W74" s="43" t="s">
+      <c r="W74" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="X74" s="54">
+      <c r="X74" s="50">
         <v>800000</v>
       </c>
-      <c r="Y74" s="54">
+      <c r="Y74" s="50">
         <v>14948.090000000002</v>
       </c>
       <c r="Z74" s="26">
@@ -10905,7 +10940,7 @@
         <v>87570.659999999916</v>
       </c>
     </row>
-    <row r="75" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" ht="117" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>74</v>
       </c>
@@ -10918,16 +10953,16 @@
       <c r="D75" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E75" s="43" t="s">
+      <c r="E75" s="40" t="s">
         <v>433</v>
       </c>
-      <c r="F75" s="43" t="s">
+      <c r="F75" s="40" t="s">
         <v>428</v>
       </c>
       <c r="G75" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H75" s="53">
+      <c r="H75" s="49">
         <v>0.43859999999999999</v>
       </c>
       <c r="I75" s="22">
@@ -10937,23 +10972,23 @@
       <c r="J75" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="K75" s="65"/>
+      <c r="K75" s="60"/>
       <c r="L75" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="M75" s="43" t="s">
+      <c r="M75" s="40" t="s">
         <v>431</v>
       </c>
       <c r="N75" s="23">
         <v>13787322</v>
       </c>
-      <c r="O75" s="43" t="s">
+      <c r="O75" s="40" t="s">
         <v>432</v>
       </c>
-      <c r="P75" s="28">
+      <c r="P75" s="74">
         <v>15.3352</v>
       </c>
-      <c r="Q75" s="28">
+      <c r="Q75" s="74">
         <v>-90.678799999999995</v>
       </c>
       <c r="R75" s="24">
@@ -10968,16 +11003,16 @@
       <c r="U75" s="23">
         <v>75</v>
       </c>
-      <c r="V75" s="43" t="s">
+      <c r="V75" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="W75" s="43" t="s">
+      <c r="W75" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="X75" s="54">
+      <c r="X75" s="50">
         <v>310000</v>
       </c>
-      <c r="Y75" s="54">
+      <c r="Y75" s="50">
         <v>-4598.6399999999994</v>
       </c>
       <c r="Z75" s="26">
@@ -10992,7 +11027,7 @@
         <v>20858.919999999984</v>
       </c>
     </row>
-    <row r="76" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" ht="117" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>75</v>
       </c>
@@ -11005,16 +11040,16 @@
       <c r="D76" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E76" s="43" t="s">
+      <c r="E76" s="40" t="s">
         <v>434</v>
       </c>
-      <c r="F76" s="43" t="s">
+      <c r="F76" s="40" t="s">
         <v>428</v>
       </c>
       <c r="G76" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H76" s="53">
+      <c r="H76" s="49">
         <v>0.52700000000000002</v>
       </c>
       <c r="I76" s="22">
@@ -11024,23 +11059,23 @@
       <c r="J76" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="K76" s="65"/>
+      <c r="K76" s="60"/>
       <c r="L76" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="M76" s="43" t="s">
+      <c r="M76" s="40" t="s">
         <v>431</v>
       </c>
       <c r="N76" s="23">
         <v>13787322</v>
       </c>
-      <c r="O76" s="43" t="s">
+      <c r="O76" s="40" t="s">
         <v>432</v>
       </c>
-      <c r="P76" s="28">
+      <c r="P76" s="74">
         <v>15.3447</v>
       </c>
-      <c r="Q76" s="28">
+      <c r="Q76" s="74">
         <v>-90.649900000000002</v>
       </c>
       <c r="R76" s="24">
@@ -11055,16 +11090,16 @@
       <c r="U76" s="23">
         <v>75</v>
       </c>
-      <c r="V76" s="43" t="s">
+      <c r="V76" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="W76" s="43" t="s">
+      <c r="W76" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="X76" s="54">
+      <c r="X76" s="50">
         <v>780000</v>
       </c>
-      <c r="Y76" s="54">
+      <c r="Y76" s="50">
         <v>182619.58000000002</v>
       </c>
       <c r="Z76" s="26">
@@ -11079,7 +11114,7 @@
         <v>103153.58000000007</v>
       </c>
     </row>
-    <row r="77" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>76</v>
       </c>
@@ -11092,16 +11127,16 @@
       <c r="D77" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E77" s="43" t="s">
+      <c r="E77" s="40" t="s">
         <v>435</v>
       </c>
-      <c r="F77" s="43" t="s">
+      <c r="F77" s="40" t="s">
         <v>428</v>
       </c>
       <c r="G77" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H77" s="53">
+      <c r="H77" s="49">
         <v>0.36630000000000001</v>
       </c>
       <c r="I77" s="22">
@@ -11111,23 +11146,23 @@
       <c r="J77" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="K77" s="65"/>
+      <c r="K77" s="60"/>
       <c r="L77" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="M77" s="43" t="s">
+      <c r="M77" s="40" t="s">
         <v>431</v>
       </c>
       <c r="N77" s="23">
         <v>13787322</v>
       </c>
-      <c r="O77" s="43" t="s">
+      <c r="O77" s="40" t="s">
         <v>432</v>
       </c>
-      <c r="P77" s="23">
+      <c r="P77" s="74">
         <v>14.8069661</v>
       </c>
-      <c r="Q77" s="23">
+      <c r="Q77" s="74">
         <v>-91.404179799999994</v>
       </c>
       <c r="R77" s="24">
@@ -11142,16 +11177,16 @@
       <c r="U77" s="23">
         <v>75</v>
       </c>
-      <c r="V77" s="43" t="s">
+      <c r="V77" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="W77" s="43" t="s">
+      <c r="W77" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="X77" s="54">
+      <c r="X77" s="50">
         <v>370000</v>
       </c>
-      <c r="Y77" s="54">
+      <c r="Y77" s="50">
         <v>102590.05</v>
       </c>
       <c r="Z77" s="26">
@@ -11166,7 +11201,7 @@
         <v>47564.630000000005</v>
       </c>
     </row>
-    <row r="78" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>77</v>
       </c>
@@ -11179,16 +11214,16 @@
       <c r="D78" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E78" s="43" t="s">
+      <c r="E78" s="40" t="s">
         <v>436</v>
       </c>
-      <c r="F78" s="43" t="s">
+      <c r="F78" s="40" t="s">
         <v>428</v>
       </c>
       <c r="G78" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H78" s="53">
+      <c r="H78" s="49">
         <v>0.2712</v>
       </c>
       <c r="I78" s="22">
@@ -11198,23 +11233,23 @@
       <c r="J78" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="K78" s="65"/>
+      <c r="K78" s="60"/>
       <c r="L78" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="M78" s="43" t="s">
+      <c r="M78" s="40" t="s">
         <v>431</v>
       </c>
       <c r="N78" s="23">
         <v>13787322</v>
       </c>
-      <c r="O78" s="43" t="s">
+      <c r="O78" s="40" t="s">
         <v>432</v>
       </c>
-      <c r="P78" s="28">
+      <c r="P78" s="74">
         <v>15.343</v>
       </c>
-      <c r="Q78" s="28">
+      <c r="Q78" s="74">
         <v>-90.668700000000001</v>
       </c>
       <c r="R78" s="24">
@@ -11229,16 +11264,16 @@
       <c r="U78" s="23">
         <v>75</v>
       </c>
-      <c r="V78" s="43" t="s">
+      <c r="V78" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="W78" s="43" t="s">
+      <c r="W78" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="X78" s="54">
+      <c r="X78" s="50">
         <v>670000</v>
       </c>
-      <c r="Y78" s="54">
+      <c r="Y78" s="50">
         <v>144611.68</v>
       </c>
       <c r="Z78" s="26">
@@ -11253,7 +11288,7 @@
         <v>83168.159999999916</v>
       </c>
     </row>
-    <row r="79" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>78</v>
       </c>
@@ -11266,16 +11301,16 @@
       <c r="D79" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E79" s="43" t="s">
+      <c r="E79" s="40" t="s">
         <v>437</v>
       </c>
-      <c r="F79" s="43" t="s">
+      <c r="F79" s="40" t="s">
         <v>438</v>
       </c>
       <c r="G79" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H79" s="53">
+      <c r="H79" s="49">
         <v>0.4002</v>
       </c>
       <c r="I79" s="22">
@@ -11285,23 +11320,23 @@
       <c r="J79" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="K79" s="63"/>
+      <c r="K79" s="58"/>
       <c r="L79" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="M79" s="43" t="s">
+      <c r="M79" s="40" t="s">
         <v>431</v>
       </c>
       <c r="N79" s="23">
         <v>13787322</v>
       </c>
-      <c r="O79" s="43" t="s">
+      <c r="O79" s="40" t="s">
         <v>432</v>
       </c>
-      <c r="P79" s="23">
+      <c r="P79" s="74">
         <v>15.200042</v>
       </c>
-      <c r="Q79" s="23">
+      <c r="Q79" s="74">
         <v>-91.212501500000002</v>
       </c>
       <c r="R79" s="24">
@@ -11316,16 +11351,16 @@
       <c r="U79" s="23">
         <v>75</v>
       </c>
-      <c r="V79" s="43" t="s">
+      <c r="V79" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="W79" s="43" t="s">
+      <c r="W79" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="X79" s="54">
+      <c r="X79" s="50">
         <v>362000</v>
       </c>
-      <c r="Y79" s="54">
+      <c r="Y79" s="50">
         <v>189468.76</v>
       </c>
       <c r="Z79" s="26">
@@ -11340,7 +11375,7 @@
         <v>57917.97000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A80" s="7">
         <v>79</v>
       </c>
@@ -11353,16 +11388,16 @@
       <c r="D80" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E80" s="43" t="s">
+      <c r="E80" s="40" t="s">
         <v>439</v>
       </c>
-      <c r="F80" s="43" t="s">
+      <c r="F80" s="40" t="s">
         <v>440</v>
       </c>
       <c r="G80" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H80" s="53">
+      <c r="H80" s="49">
         <v>0.1168</v>
       </c>
       <c r="I80" s="22">
@@ -11372,25 +11407,25 @@
       <c r="J80" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="K80" s="62" t="s">
+      <c r="K80" s="57" t="s">
         <v>442</v>
       </c>
       <c r="L80" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="M80" s="56" t="s">
+      <c r="M80" s="52" t="s">
         <v>404</v>
       </c>
       <c r="N80" s="23">
         <v>16423089</v>
       </c>
-      <c r="O80" s="53" t="s">
+      <c r="O80" s="49" t="s">
         <v>443</v>
       </c>
-      <c r="P80" s="23">
+      <c r="P80" s="74">
         <v>15.7391659</v>
       </c>
-      <c r="Q80" s="23">
+      <c r="Q80" s="74">
         <v>-91.112996300000006</v>
       </c>
       <c r="R80" s="24">
@@ -11405,16 +11440,16 @@
       <c r="U80" s="23">
         <v>90</v>
       </c>
-      <c r="V80" s="53" t="s">
+      <c r="V80" s="49" t="s">
         <v>444</v>
       </c>
-      <c r="W80" s="53" t="s">
+      <c r="W80" s="49" t="s">
         <v>445</v>
       </c>
-      <c r="X80" s="54">
+      <c r="X80" s="50">
         <v>824225.4</v>
       </c>
-      <c r="Y80" s="54">
+      <c r="Y80" s="50">
         <v>56512.01999999999</v>
       </c>
       <c r="Z80" s="26">
@@ -11429,7 +11464,7 @@
         <v>88223.030000000028</v>
       </c>
     </row>
-    <row r="81" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
         <v>80</v>
       </c>
@@ -11442,16 +11477,16 @@
       <c r="D81" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E81" s="43" t="s">
+      <c r="E81" s="40" t="s">
         <v>446</v>
       </c>
-      <c r="F81" s="43" t="s">
+      <c r="F81" s="40" t="s">
         <v>440</v>
       </c>
       <c r="G81" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H81" s="53">
+      <c r="H81" s="49">
         <v>0.36</v>
       </c>
       <c r="I81" s="22">
@@ -11461,23 +11496,23 @@
       <c r="J81" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="K81" s="65"/>
+      <c r="K81" s="60"/>
       <c r="L81" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="M81" s="56" t="s">
+      <c r="M81" s="52" t="s">
         <v>404</v>
       </c>
       <c r="N81" s="23">
         <v>16423089</v>
       </c>
-      <c r="O81" s="53" t="s">
+      <c r="O81" s="49" t="s">
         <v>443</v>
       </c>
-      <c r="P81" s="23">
+      <c r="P81" s="74">
         <v>15.6955157</v>
       </c>
-      <c r="Q81" s="23">
+      <c r="Q81" s="74">
         <v>-90.986187000000001</v>
       </c>
       <c r="R81" s="24">
@@ -11492,16 +11527,16 @@
       <c r="U81" s="23">
         <v>90</v>
       </c>
-      <c r="V81" s="53" t="s">
+      <c r="V81" s="49" t="s">
         <v>444</v>
       </c>
-      <c r="W81" s="53" t="s">
+      <c r="W81" s="49" t="s">
         <v>445</v>
       </c>
-      <c r="X81" s="54">
+      <c r="X81" s="50">
         <v>826582.96</v>
       </c>
-      <c r="Y81" s="54">
+      <c r="Y81" s="50">
         <v>619059.93000000005</v>
       </c>
       <c r="Z81" s="26">
@@ -11516,7 +11551,7 @@
         <v>144638.80000000005</v>
       </c>
     </row>
-    <row r="82" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A82" s="7">
         <v>81</v>
       </c>
@@ -11529,16 +11564,16 @@
       <c r="D82" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E82" s="43" t="s">
+      <c r="E82" s="40" t="s">
         <v>447</v>
       </c>
-      <c r="F82" s="43" t="s">
+      <c r="F82" s="40" t="s">
         <v>440</v>
       </c>
       <c r="G82" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H82" s="53">
+      <c r="H82" s="49">
         <v>0.19769999999999999</v>
       </c>
       <c r="I82" s="22">
@@ -11548,23 +11583,23 @@
       <c r="J82" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="K82" s="65"/>
+      <c r="K82" s="60"/>
       <c r="L82" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="M82" s="56" t="s">
+      <c r="M82" s="52" t="s">
         <v>404</v>
       </c>
       <c r="N82" s="23">
         <v>16423089</v>
       </c>
-      <c r="O82" s="53" t="s">
+      <c r="O82" s="49" t="s">
         <v>443</v>
       </c>
-      <c r="P82" s="23">
+      <c r="P82" s="74">
         <v>15.664338000000001</v>
       </c>
-      <c r="Q82" s="23">
+      <c r="Q82" s="74">
         <v>-91.073359600000003</v>
       </c>
       <c r="R82" s="24">
@@ -11579,16 +11614,16 @@
       <c r="U82" s="23">
         <v>90</v>
       </c>
-      <c r="V82" s="53" t="s">
+      <c r="V82" s="49" t="s">
         <v>444</v>
       </c>
-      <c r="W82" s="53" t="s">
+      <c r="W82" s="49" t="s">
         <v>445</v>
       </c>
-      <c r="X82" s="54">
+      <c r="X82" s="50">
         <v>1089623.24</v>
       </c>
-      <c r="Y82" s="54">
+      <c r="Y82" s="50">
         <v>0</v>
       </c>
       <c r="Z82" s="26">
@@ -11603,7 +11638,7 @@
         <v>108978.08999999997</v>
       </c>
     </row>
-    <row r="83" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
         <v>82</v>
       </c>
@@ -11616,16 +11651,16 @@
       <c r="D83" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E83" s="43" t="s">
+      <c r="E83" s="40" t="s">
         <v>448</v>
       </c>
-      <c r="F83" s="43" t="s">
+      <c r="F83" s="40" t="s">
         <v>440</v>
       </c>
       <c r="G83" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H83" s="53">
+      <c r="H83" s="49">
         <v>0.2893</v>
       </c>
       <c r="I83" s="22">
@@ -11635,23 +11670,23 @@
       <c r="J83" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="K83" s="63"/>
+      <c r="K83" s="58"/>
       <c r="L83" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="M83" s="56" t="s">
+      <c r="M83" s="52" t="s">
         <v>404</v>
       </c>
       <c r="N83" s="23">
         <v>16423089</v>
       </c>
-      <c r="O83" s="53" t="s">
+      <c r="O83" s="49" t="s">
         <v>443</v>
       </c>
-      <c r="P83" s="23">
+      <c r="P83" s="74">
         <v>15.697703600000001</v>
       </c>
-      <c r="Q83" s="23">
+      <c r="Q83" s="74">
         <v>-91.154928999999996</v>
       </c>
       <c r="R83" s="24">
@@ -11666,16 +11701,16 @@
       <c r="U83" s="23">
         <v>90</v>
       </c>
-      <c r="V83" s="53" t="s">
+      <c r="V83" s="49" t="s">
         <v>444</v>
       </c>
-      <c r="W83" s="53" t="s">
+      <c r="W83" s="49" t="s">
         <v>445</v>
       </c>
-      <c r="X83" s="54">
+      <c r="X83" s="50">
         <v>637449.23</v>
       </c>
-      <c r="Y83" s="54">
+      <c r="Y83" s="50">
         <v>0</v>
       </c>
       <c r="Z83" s="26">
@@ -11690,7 +11725,7 @@
         <v>63786.109999999986</v>
       </c>
     </row>
-    <row r="84" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A84" s="7">
         <v>83</v>
       </c>
@@ -11703,16 +11738,16 @@
       <c r="D84" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="43" t="s">
+      <c r="E84" s="40" t="s">
         <v>449</v>
       </c>
-      <c r="F84" s="43" t="s">
+      <c r="F84" s="40" t="s">
         <v>450</v>
       </c>
       <c r="G84" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H84" s="53">
+      <c r="H84" s="49">
         <v>0.53569999999999995</v>
       </c>
       <c r="I84" s="22">
@@ -11722,25 +11757,25 @@
       <c r="J84" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="K84" s="62" t="s">
+      <c r="K84" s="57" t="s">
         <v>452</v>
       </c>
       <c r="L84" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="M84" s="43" t="s">
+      <c r="M84" s="40" t="s">
         <v>404</v>
       </c>
       <c r="N84" s="23">
         <v>19372116</v>
       </c>
-      <c r="O84" s="53" t="s">
+      <c r="O84" s="49" t="s">
         <v>453</v>
       </c>
-      <c r="P84" s="23">
+      <c r="P84" s="74">
         <v>15.4077561</v>
       </c>
-      <c r="Q84" s="23">
+      <c r="Q84" s="74">
         <v>-91.155741800000001</v>
       </c>
       <c r="R84" s="24">
@@ -11755,16 +11790,16 @@
       <c r="U84" s="23">
         <v>0</v>
       </c>
-      <c r="V84" s="53" t="s">
+      <c r="V84" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="W84" s="43" t="s">
+      <c r="W84" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="X84" s="54">
+      <c r="X84" s="50">
         <v>2337257.65</v>
       </c>
-      <c r="Y84" s="54">
+      <c r="Y84" s="50">
         <v>1374734.67</v>
       </c>
       <c r="Z84" s="26">
@@ -11779,7 +11814,7 @@
         <v>373272.7799999998</v>
       </c>
     </row>
-    <row r="85" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
         <v>84</v>
       </c>
@@ -11792,16 +11827,16 @@
       <c r="D85" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E85" s="43" t="s">
+      <c r="E85" s="40" t="s">
         <v>454</v>
       </c>
-      <c r="F85" s="43" t="s">
+      <c r="F85" s="40" t="s">
         <v>450</v>
       </c>
       <c r="G85" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H85" s="53">
+      <c r="H85" s="49">
         <v>0.3987</v>
       </c>
       <c r="I85" s="22">
@@ -11811,23 +11846,23 @@
       <c r="J85" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="K85" s="65"/>
+      <c r="K85" s="60"/>
       <c r="L85" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="M85" s="43" t="s">
+      <c r="M85" s="40" t="s">
         <v>404</v>
       </c>
       <c r="N85" s="23">
         <v>19372116</v>
       </c>
-      <c r="O85" s="53" t="s">
+      <c r="O85" s="49" t="s">
         <v>453</v>
       </c>
-      <c r="P85" s="23">
+      <c r="P85" s="74">
         <v>15.5564286</v>
       </c>
-      <c r="Q85" s="23">
+      <c r="Q85" s="74">
         <v>-91.124447099999998</v>
       </c>
       <c r="R85" s="24">
@@ -11842,16 +11877,16 @@
       <c r="U85" s="23">
         <v>0</v>
       </c>
-      <c r="V85" s="53" t="s">
+      <c r="V85" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="W85" s="43" t="s">
+      <c r="W85" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="X85" s="54">
+      <c r="X85" s="50">
         <v>1096134.48</v>
       </c>
-      <c r="Y85" s="54">
+      <c r="Y85" s="50">
         <v>124740.01</v>
       </c>
       <c r="Z85" s="26">
@@ -11866,7 +11901,7 @@
         <v>122847.1100000001</v>
       </c>
     </row>
-    <row r="86" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
         <v>85</v>
       </c>
@@ -11879,16 +11914,16 @@
       <c r="D86" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E86" s="43" t="s">
+      <c r="E86" s="40" t="s">
         <v>455</v>
       </c>
-      <c r="F86" s="43" t="s">
+      <c r="F86" s="40" t="s">
         <v>450</v>
       </c>
       <c r="G86" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H86" s="53">
+      <c r="H86" s="49">
         <v>0.15179999999999999</v>
       </c>
       <c r="I86" s="22">
@@ -11898,23 +11933,23 @@
       <c r="J86" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="K86" s="65"/>
+      <c r="K86" s="60"/>
       <c r="L86" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="M86" s="43" t="s">
+      <c r="M86" s="40" t="s">
         <v>404</v>
       </c>
       <c r="N86" s="23">
         <v>19372116</v>
       </c>
-      <c r="O86" s="53" t="s">
+      <c r="O86" s="49" t="s">
         <v>453</v>
       </c>
-      <c r="P86" s="23">
+      <c r="P86" s="74">
         <v>15.5151763</v>
       </c>
-      <c r="Q86" s="23">
+      <c r="Q86" s="74">
         <v>-91.290671900000007</v>
       </c>
       <c r="R86" s="24">
@@ -11929,16 +11964,16 @@
       <c r="U86" s="23">
         <v>0</v>
       </c>
-      <c r="V86" s="53" t="s">
+      <c r="V86" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="W86" s="43" t="s">
+      <c r="W86" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="X86" s="54">
+      <c r="X86" s="50">
         <v>970204.85</v>
       </c>
-      <c r="Y86" s="54">
+      <c r="Y86" s="50">
         <v>305450.36</v>
       </c>
       <c r="Z86" s="26">
@@ -11953,7 +11988,7 @@
         <v>128109.30000000005</v>
       </c>
     </row>
-    <row r="87" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
         <v>86</v>
       </c>
@@ -11966,16 +12001,16 @@
       <c r="D87" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E87" s="43" t="s">
+      <c r="E87" s="40" t="s">
         <v>456</v>
       </c>
-      <c r="F87" s="43" t="s">
+      <c r="F87" s="40" t="s">
         <v>457</v>
       </c>
       <c r="G87" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H87" s="53">
+      <c r="H87" s="49">
         <v>0.34360000000000002</v>
       </c>
       <c r="I87" s="22">
@@ -11985,23 +12020,23 @@
       <c r="J87" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="K87" s="63"/>
+      <c r="K87" s="58"/>
       <c r="L87" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="M87" s="43" t="s">
+      <c r="M87" s="40" t="s">
         <v>404</v>
       </c>
       <c r="N87" s="23">
         <v>19372116</v>
       </c>
-      <c r="O87" s="53" t="s">
+      <c r="O87" s="49" t="s">
         <v>453</v>
       </c>
-      <c r="P87" s="23">
+      <c r="P87" s="74">
         <v>15.8675997</v>
       </c>
-      <c r="Q87" s="23">
+      <c r="Q87" s="74">
         <v>-90.887016200000005</v>
       </c>
       <c r="R87" s="24">
@@ -12016,16 +12051,16 @@
       <c r="U87" s="23">
         <v>0</v>
       </c>
-      <c r="V87" s="53" t="s">
+      <c r="V87" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="W87" s="43" t="s">
+      <c r="W87" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="X87" s="54">
+      <c r="X87" s="50">
         <v>1166403.02</v>
       </c>
-      <c r="Y87" s="54">
+      <c r="Y87" s="50">
         <v>422607.73</v>
       </c>
       <c r="Z87" s="26">
@@ -12040,7 +12075,7 @@
         <v>159076.07000000007</v>
       </c>
     </row>
-    <row r="88" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" ht="117" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
         <v>87</v>
       </c>
@@ -12053,16 +12088,16 @@
       <c r="D88" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E88" s="43" t="s">
+      <c r="E88" s="40" t="s">
         <v>458</v>
       </c>
-      <c r="F88" s="43" t="s">
+      <c r="F88" s="40" t="s">
         <v>428</v>
       </c>
       <c r="G88" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H88" s="53">
+      <c r="H88" s="49">
         <v>0.1</v>
       </c>
       <c r="I88" s="22">
@@ -12072,25 +12107,25 @@
       <c r="J88" s="21" t="s">
         <v>459</v>
       </c>
-      <c r="K88" s="62" t="s">
+      <c r="K88" s="57" t="s">
         <v>460</v>
       </c>
       <c r="L88" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="M88" s="43" t="s">
+      <c r="M88" s="40" t="s">
         <v>461</v>
       </c>
       <c r="N88" s="23">
         <v>19375255</v>
       </c>
-      <c r="O88" s="53" t="s">
+      <c r="O88" s="49" t="s">
         <v>462</v>
       </c>
-      <c r="P88" s="28">
+      <c r="P88" s="74">
         <v>15.3447</v>
       </c>
-      <c r="Q88" s="28">
+      <c r="Q88" s="74">
         <v>-90.770600000000002</v>
       </c>
       <c r="R88" s="24">
@@ -12105,22 +12140,22 @@
       <c r="U88" s="23">
         <v>0</v>
       </c>
-      <c r="V88" s="53" t="s">
+      <c r="V88" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="W88" s="43" t="s">
+      <c r="W88" s="40" t="s">
         <v>392</v>
       </c>
-      <c r="X88" s="54">
+      <c r="X88" s="50">
         <v>1333872.17</v>
       </c>
-      <c r="Y88" s="54">
-        <v>0</v>
-      </c>
-      <c r="Z88" s="54">
+      <c r="Y88" s="50">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="50">
         <v>1333872.17</v>
       </c>
-      <c r="AA88" s="54">
+      <c r="AA88" s="50">
         <v>0</v>
       </c>
       <c r="AB88" s="27">
@@ -12128,7 +12163,7 @@
         <v>1333872.17</v>
       </c>
     </row>
-    <row r="89" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
         <v>88</v>
       </c>
@@ -12141,16 +12176,16 @@
       <c r="D89" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E89" s="43" t="s">
+      <c r="E89" s="40" t="s">
         <v>463</v>
       </c>
-      <c r="F89" s="43" t="s">
+      <c r="F89" s="40" t="s">
         <v>464</v>
       </c>
       <c r="G89" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H89" s="53">
+      <c r="H89" s="49">
         <v>0</v>
       </c>
       <c r="I89" s="22">
@@ -12160,23 +12195,23 @@
       <c r="J89" s="21" t="s">
         <v>459</v>
       </c>
-      <c r="K89" s="63"/>
+      <c r="K89" s="58"/>
       <c r="L89" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="M89" s="43" t="s">
+      <c r="M89" s="40" t="s">
         <v>461</v>
       </c>
       <c r="N89" s="23">
         <v>19375255</v>
       </c>
-      <c r="O89" s="53" t="s">
+      <c r="O89" s="49" t="s">
         <v>462</v>
       </c>
-      <c r="P89" s="28">
+      <c r="P89" s="74">
         <v>15.234500000000001</v>
       </c>
-      <c r="Q89" s="28">
+      <c r="Q89" s="74">
         <v>-91.116799999999998</v>
       </c>
       <c r="R89" s="24">
@@ -12191,22 +12226,22 @@
       <c r="U89" s="23">
         <v>0</v>
       </c>
-      <c r="V89" s="53" t="s">
+      <c r="V89" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="W89" s="43" t="s">
+      <c r="W89" s="40" t="s">
         <v>392</v>
       </c>
-      <c r="X89" s="54">
+      <c r="X89" s="50">
         <v>1316323.52</v>
       </c>
-      <c r="Y89" s="54">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="54">
+      <c r="Y89" s="50">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="50">
         <v>1316323.52</v>
       </c>
-      <c r="AA89" s="54">
+      <c r="AA89" s="50">
         <v>0</v>
       </c>
       <c r="AB89" s="27">
@@ -12214,29 +12249,29 @@
         <v>1316323.52</v>
       </c>
     </row>
-    <row r="90" spans="1:28" ht="273" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
         <v>89</v>
       </c>
-      <c r="B90" s="67">
+      <c r="B90" s="62">
         <v>2022</v>
       </c>
-      <c r="C90" s="67" t="s">
+      <c r="C90" s="62" t="s">
         <v>56</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E90" s="37" t="s">
+      <c r="E90" s="34" t="s">
         <v>465</v>
       </c>
-      <c r="F90" s="37" t="s">
+      <c r="F90" s="34" t="s">
         <v>466</v>
       </c>
-      <c r="G90" s="37" t="s">
+      <c r="G90" s="34" t="s">
         <v>264</v>
       </c>
-      <c r="H90" s="38">
+      <c r="H90" s="35">
         <v>0.29199999999999998</v>
       </c>
       <c r="I90" s="10">
@@ -12246,31 +12281,31 @@
       <c r="J90" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K90" s="59" t="s">
+      <c r="K90" s="55" t="s">
         <v>467</v>
       </c>
       <c r="L90" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="M90" s="49" t="s">
+      <c r="M90" s="45" t="s">
         <v>468</v>
       </c>
       <c r="N90" s="12">
         <v>18490697</v>
       </c>
-      <c r="O90" s="37" t="s">
+      <c r="O90" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="P90" s="31">
+      <c r="P90" s="73">
         <v>15.069699999999999</v>
       </c>
-      <c r="Q90" s="31">
+      <c r="Q90" s="73">
         <v>-91.710999999999999</v>
       </c>
-      <c r="R90" s="68">
+      <c r="R90" s="63">
         <v>44893</v>
       </c>
-      <c r="S90" s="68">
+      <c r="S90" s="63">
         <v>44982</v>
       </c>
       <c r="T90" s="12">
@@ -12279,16 +12314,16 @@
       <c r="U90" s="12">
         <v>90</v>
       </c>
-      <c r="V90" s="58" t="s">
+      <c r="V90" s="54" t="s">
         <v>470</v>
       </c>
-      <c r="W90" s="58" t="s">
+      <c r="W90" s="54" t="s">
         <v>471</v>
       </c>
-      <c r="X90" s="52">
+      <c r="X90" s="48">
         <v>2003100.14</v>
       </c>
-      <c r="Y90" s="52">
+      <c r="Y90" s="48">
         <f>40603.64+407141.82+519507.4+18902.94</f>
         <v>986155.8</v>
       </c>
@@ -12304,29 +12339,29 @@
         <v>783612.96999999974</v>
       </c>
     </row>
-    <row r="91" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
         <v>90</v>
       </c>
-      <c r="B91" s="67">
+      <c r="B91" s="62">
         <v>2022</v>
       </c>
-      <c r="C91" s="67" t="s">
+      <c r="C91" s="62" t="s">
         <v>56</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E91" s="37" t="s">
+      <c r="E91" s="34" t="s">
         <v>472</v>
       </c>
-      <c r="F91" s="37" t="s">
+      <c r="F91" s="34" t="s">
         <v>466</v>
       </c>
-      <c r="G91" s="37" t="s">
+      <c r="G91" s="34" t="s">
         <v>264</v>
       </c>
-      <c r="H91" s="38">
+      <c r="H91" s="35">
         <v>0.44040000000000001</v>
       </c>
       <c r="I91" s="10">
@@ -12336,23 +12371,23 @@
       <c r="J91" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K91" s="60"/>
+      <c r="K91" s="56"/>
       <c r="L91" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="M91" s="49" t="s">
+      <c r="M91" s="45" t="s">
         <v>468</v>
       </c>
       <c r="N91" s="12">
         <v>18490697</v>
       </c>
-      <c r="O91" s="37" t="s">
+      <c r="O91" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="P91" s="31">
+      <c r="P91" s="73">
         <v>15.187900000000001</v>
       </c>
-      <c r="Q91" s="31">
+      <c r="Q91" s="73">
         <v>-91.760499999999993</v>
       </c>
       <c r="R91" s="14">
@@ -12367,16 +12402,16 @@
       <c r="U91" s="12">
         <v>90</v>
       </c>
-      <c r="V91" s="58" t="s">
+      <c r="V91" s="54" t="s">
         <v>470</v>
       </c>
-      <c r="W91" s="58" t="s">
+      <c r="W91" s="54" t="s">
         <v>471</v>
       </c>
-      <c r="X91" s="52">
+      <c r="X91" s="48">
         <v>1877315.91</v>
       </c>
-      <c r="Y91" s="52">
+      <c r="Y91" s="48">
         <f>30576.44+244951.33+91916</f>
         <v>367443.76999999996</v>
       </c>
@@ -12392,7 +12427,7 @@
         <v>307174.08999999962</v>
       </c>
     </row>
-    <row r="92" spans="1:28" ht="273" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
         <v>91</v>
       </c>
@@ -12405,16 +12440,16 @@
       <c r="D92" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E92" s="43" t="s">
+      <c r="E92" s="40" t="s">
         <v>473</v>
       </c>
-      <c r="F92" s="43" t="s">
+      <c r="F92" s="40" t="s">
         <v>474</v>
       </c>
-      <c r="G92" s="43" t="s">
+      <c r="G92" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="H92" s="53">
+      <c r="H92" s="49">
         <v>0.21</v>
       </c>
       <c r="I92" s="22">
@@ -12424,25 +12459,25 @@
       <c r="J92" s="21" t="s">
         <v>475</v>
       </c>
-      <c r="K92" s="62" t="s">
+      <c r="K92" s="57" t="s">
         <v>476</v>
       </c>
       <c r="L92" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="M92" s="56" t="s">
+      <c r="M92" s="52" t="s">
         <v>477</v>
       </c>
       <c r="N92" s="23">
         <v>18490700</v>
       </c>
-      <c r="O92" s="43" t="s">
+      <c r="O92" s="40" t="s">
         <v>478</v>
       </c>
-      <c r="P92" s="28">
+      <c r="P92" s="74">
         <v>15.289400000000001</v>
       </c>
-      <c r="Q92" s="28">
+      <c r="Q92" s="74">
         <v>-91.805700000000002</v>
       </c>
       <c r="R92" s="24">
@@ -12457,16 +12492,16 @@
       <c r="U92" s="23">
         <v>296</v>
       </c>
-      <c r="V92" s="43" t="s">
+      <c r="V92" s="40" t="s">
         <v>479</v>
       </c>
-      <c r="W92" s="43" t="s">
+      <c r="W92" s="40" t="s">
         <v>480</v>
       </c>
-      <c r="X92" s="54">
+      <c r="X92" s="50">
         <v>2306141.38</v>
       </c>
-      <c r="Y92" s="54">
+      <c r="Y92" s="50">
         <v>1030353.56</v>
       </c>
       <c r="Z92" s="26">
@@ -12481,7 +12516,7 @@
         <v>333561.58999999985</v>
       </c>
     </row>
-    <row r="93" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
         <v>92</v>
       </c>
@@ -12494,16 +12529,16 @@
       <c r="D93" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E93" s="43" t="s">
+      <c r="E93" s="40" t="s">
         <v>481</v>
       </c>
-      <c r="F93" s="43" t="s">
+      <c r="F93" s="40" t="s">
         <v>474</v>
       </c>
-      <c r="G93" s="43" t="s">
+      <c r="G93" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="H93" s="53">
+      <c r="H93" s="49">
         <v>0.9</v>
       </c>
       <c r="I93" s="22">
@@ -12513,23 +12548,23 @@
       <c r="J93" s="21" t="s">
         <v>475</v>
       </c>
-      <c r="K93" s="65"/>
+      <c r="K93" s="60"/>
       <c r="L93" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="M93" s="56" t="s">
+      <c r="M93" s="52" t="s">
         <v>477</v>
       </c>
       <c r="N93" s="23">
         <v>18490700</v>
       </c>
-      <c r="O93" s="43" t="s">
+      <c r="O93" s="40" t="s">
         <v>478</v>
       </c>
-      <c r="P93" s="28">
+      <c r="P93" s="74">
         <v>15.2654</v>
       </c>
-      <c r="Q93" s="28">
+      <c r="Q93" s="74">
         <v>-91.951099999999997</v>
       </c>
       <c r="R93" s="24">
@@ -12544,16 +12579,16 @@
       <c r="U93" s="23">
         <v>296</v>
       </c>
-      <c r="V93" s="43" t="s">
+      <c r="V93" s="40" t="s">
         <v>479</v>
       </c>
-      <c r="W93" s="43" t="s">
+      <c r="W93" s="40" t="s">
         <v>480</v>
       </c>
-      <c r="X93" s="54">
+      <c r="X93" s="50">
         <v>1289770.33</v>
       </c>
-      <c r="Y93" s="54">
+      <c r="Y93" s="50">
         <v>426046.22</v>
       </c>
       <c r="Z93" s="26">
@@ -12568,7 +12603,7 @@
         <v>171654.85000000009</v>
       </c>
     </row>
-    <row r="94" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
         <v>93</v>
       </c>
@@ -12581,16 +12616,16 @@
       <c r="D94" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E94" s="43" t="s">
+      <c r="E94" s="40" t="s">
         <v>482</v>
       </c>
-      <c r="F94" s="43" t="s">
+      <c r="F94" s="40" t="s">
         <v>474</v>
       </c>
-      <c r="G94" s="43" t="s">
+      <c r="G94" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="H94" s="53">
+      <c r="H94" s="49">
         <v>0.57999999999999996</v>
       </c>
       <c r="I94" s="22">
@@ -12600,23 +12635,23 @@
       <c r="J94" s="21" t="s">
         <v>475</v>
       </c>
-      <c r="K94" s="63"/>
+      <c r="K94" s="58"/>
       <c r="L94" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="M94" s="56" t="s">
+      <c r="M94" s="52" t="s">
         <v>477</v>
       </c>
       <c r="N94" s="23">
         <v>18490700</v>
       </c>
-      <c r="O94" s="43" t="s">
+      <c r="O94" s="40" t="s">
         <v>478</v>
       </c>
-      <c r="P94" s="28">
+      <c r="P94" s="74">
         <v>15.2362</v>
       </c>
-      <c r="Q94" s="28">
+      <c r="Q94" s="74">
         <v>-91.918499999999995</v>
       </c>
       <c r="R94" s="24">
@@ -12631,16 +12666,16 @@
       <c r="U94" s="23">
         <v>296</v>
       </c>
-      <c r="V94" s="43" t="s">
+      <c r="V94" s="40" t="s">
         <v>479</v>
       </c>
-      <c r="W94" s="43" t="s">
+      <c r="W94" s="40" t="s">
         <v>480</v>
       </c>
-      <c r="X94" s="54">
+      <c r="X94" s="50">
         <v>2341568.96</v>
       </c>
-      <c r="Y94" s="54">
+      <c r="Y94" s="50">
         <v>868149.23</v>
       </c>
       <c r="Z94" s="26">
@@ -12655,7 +12690,7 @@
         <v>321008.00999999978</v>
       </c>
     </row>
-    <row r="95" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" ht="312" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
         <v>94</v>
       </c>
@@ -12668,16 +12703,16 @@
       <c r="D95" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E95" s="37" t="s">
+      <c r="E95" s="34" t="s">
         <v>483</v>
       </c>
-      <c r="F95" s="37" t="s">
+      <c r="F95" s="34" t="s">
         <v>484</v>
       </c>
-      <c r="G95" s="37" t="s">
+      <c r="G95" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="H95" s="38">
+      <c r="H95" s="35">
         <v>1</v>
       </c>
       <c r="I95" s="10">
@@ -12692,19 +12727,19 @@
       <c r="L95" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="M95" s="57" t="s">
+      <c r="M95" s="53" t="s">
         <v>276</v>
       </c>
       <c r="N95" s="12">
         <v>19312121</v>
       </c>
-      <c r="O95" s="50" t="s">
+      <c r="O95" s="46" t="s">
         <v>488</v>
       </c>
-      <c r="P95" s="31">
+      <c r="P95" s="73">
         <v>14.754</v>
       </c>
-      <c r="Q95" s="31">
+      <c r="Q95" s="73">
         <v>-90.411900000000003</v>
       </c>
       <c r="R95" s="14">
@@ -12719,16 +12754,16 @@
       <c r="U95" s="12">
         <v>0</v>
       </c>
-      <c r="V95" s="51" t="s">
+      <c r="V95" s="47" t="s">
         <v>489</v>
       </c>
-      <c r="W95" s="58" t="s">
+      <c r="W95" s="54" t="s">
         <v>490</v>
       </c>
-      <c r="X95" s="52">
+      <c r="X95" s="48">
         <v>1585507.67</v>
       </c>
-      <c r="Y95" s="52">
+      <c r="Y95" s="48">
         <v>0</v>
       </c>
       <c r="Z95" s="18">
@@ -12743,7 +12778,7 @@
         <v>182921.18999999994</v>
       </c>
     </row>
-    <row r="96" spans="1:28" ht="273" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
         <v>95</v>
       </c>
@@ -12756,44 +12791,44 @@
       <c r="D96" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E96" s="37" t="s">
+      <c r="E96" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="F96" s="37" t="s">
+      <c r="F96" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="G96" s="37" t="s">
+      <c r="G96" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="H96" s="38">
+      <c r="H96" s="35">
         <v>0.75</v>
       </c>
       <c r="I96" s="10">
         <f t="shared" si="11"/>
         <v>0.58633127444560695</v>
       </c>
-      <c r="J96" s="59" t="s">
+      <c r="J96" s="55" t="s">
         <v>493</v>
       </c>
-      <c r="K96" s="59" t="s">
+      <c r="K96" s="55" t="s">
         <v>494</v>
       </c>
       <c r="L96" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M96" s="57" t="s">
+      <c r="M96" s="53" t="s">
         <v>495</v>
       </c>
       <c r="N96" s="12">
         <v>19372779</v>
       </c>
-      <c r="O96" s="50" t="s">
+      <c r="O96" s="46" t="s">
         <v>496</v>
       </c>
-      <c r="P96" s="31">
+      <c r="P96" s="73">
         <v>14.8436</v>
       </c>
-      <c r="Q96" s="31">
+      <c r="Q96" s="73">
         <v>-89.8215</v>
       </c>
       <c r="R96" s="14">
@@ -12808,16 +12843,16 @@
       <c r="U96" s="12">
         <v>0</v>
       </c>
-      <c r="V96" s="51" t="s">
+      <c r="V96" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="W96" s="58" t="s">
+      <c r="W96" s="54" t="s">
         <v>304</v>
       </c>
-      <c r="X96" s="52">
+      <c r="X96" s="48">
         <v>300225.21000000002</v>
       </c>
-      <c r="Y96" s="52">
+      <c r="Y96" s="48">
         <v>0</v>
       </c>
       <c r="Z96" s="16">
@@ -12832,7 +12867,7 @@
         <v>124193.78000000003</v>
       </c>
     </row>
-    <row r="97" spans="1:28" ht="156" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:28" ht="117" x14ac:dyDescent="0.25">
       <c r="A97" s="7">
         <v>96</v>
       </c>
@@ -12845,40 +12880,40 @@
       <c r="D97" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E97" s="37" t="s">
+      <c r="E97" s="34" t="s">
         <v>497</v>
       </c>
-      <c r="F97" s="37" t="s">
+      <c r="F97" s="34" t="s">
         <v>498</v>
       </c>
-      <c r="G97" s="37" t="s">
+      <c r="G97" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="H97" s="38">
+      <c r="H97" s="35">
         <v>0.9</v>
       </c>
       <c r="I97" s="10">
         <f t="shared" si="11"/>
         <v>0.7092588187527249</v>
       </c>
-      <c r="J97" s="64"/>
-      <c r="K97" s="64"/>
+      <c r="J97" s="59"/>
+      <c r="K97" s="59"/>
       <c r="L97" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M97" s="57" t="s">
+      <c r="M97" s="53" t="s">
         <v>495</v>
       </c>
       <c r="N97" s="12">
         <v>19372779</v>
       </c>
-      <c r="O97" s="50" t="s">
+      <c r="O97" s="46" t="s">
         <v>496</v>
       </c>
-      <c r="P97" s="31">
+      <c r="P97" s="73">
         <v>14.8811</v>
       </c>
-      <c r="Q97" s="31">
+      <c r="Q97" s="73">
         <v>-89.6845</v>
       </c>
       <c r="R97" s="14">
@@ -12893,16 +12928,16 @@
       <c r="U97" s="12">
         <v>0</v>
       </c>
-      <c r="V97" s="51" t="s">
+      <c r="V97" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="W97" s="58" t="s">
+      <c r="W97" s="54" t="s">
         <v>304</v>
       </c>
-      <c r="X97" s="52">
+      <c r="X97" s="48">
         <v>1648102.68</v>
       </c>
-      <c r="Y97" s="52">
+      <c r="Y97" s="48">
         <v>0</v>
       </c>
       <c r="Z97" s="16">
@@ -12917,7 +12952,7 @@
         <v>479171.31999999983</v>
       </c>
     </row>
-    <row r="98" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:28" ht="117" x14ac:dyDescent="0.25">
       <c r="A98" s="7">
         <v>97</v>
       </c>
@@ -12930,40 +12965,40 @@
       <c r="D98" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E98" s="37" t="s">
+      <c r="E98" s="34" t="s">
         <v>499</v>
       </c>
-      <c r="F98" s="37" t="s">
+      <c r="F98" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="G98" s="37" t="s">
+      <c r="G98" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="H98" s="38">
+      <c r="H98" s="35">
         <v>0.2</v>
       </c>
       <c r="I98" s="10">
         <f t="shared" si="11"/>
         <v>0.59006930703875238</v>
       </c>
-      <c r="J98" s="60"/>
-      <c r="K98" s="60"/>
+      <c r="J98" s="56"/>
+      <c r="K98" s="56"/>
       <c r="L98" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M98" s="57" t="s">
+      <c r="M98" s="53" t="s">
         <v>495</v>
       </c>
       <c r="N98" s="12">
         <v>19372779</v>
       </c>
-      <c r="O98" s="50" t="s">
+      <c r="O98" s="46" t="s">
         <v>496</v>
       </c>
-      <c r="P98" s="36">
+      <c r="P98" s="75">
         <v>14.967700000000001</v>
       </c>
-      <c r="Q98" s="36">
+      <c r="Q98" s="75">
         <v>-89.363100000000003</v>
       </c>
       <c r="R98" s="14">
@@ -12978,16 +13013,16 @@
       <c r="U98" s="12">
         <v>0</v>
       </c>
-      <c r="V98" s="51" t="s">
+      <c r="V98" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="W98" s="58" t="s">
+      <c r="W98" s="54" t="s">
         <v>304</v>
       </c>
-      <c r="X98" s="52">
+      <c r="X98" s="48">
         <v>734837.34</v>
       </c>
-      <c r="Y98" s="52">
+      <c r="Y98" s="48">
         <v>0</v>
       </c>
       <c r="Z98" s="16">
@@ -13002,7 +13037,7 @@
         <v>301232.37999999995</v>
       </c>
     </row>
-    <row r="99" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A99" s="7">
         <v>98</v>
       </c>
@@ -13015,16 +13050,16 @@
       <c r="D99" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E99" s="37" t="s">
+      <c r="E99" s="34" t="s">
         <v>500</v>
       </c>
-      <c r="F99" s="37" t="s">
+      <c r="F99" s="34" t="s">
         <v>501</v>
       </c>
-      <c r="G99" s="37" t="s">
+      <c r="G99" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="H99" s="38">
+      <c r="H99" s="35">
         <v>1</v>
       </c>
       <c r="I99" s="10">
@@ -13040,19 +13075,19 @@
       <c r="L99" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="M99" s="37" t="s">
+      <c r="M99" s="34" t="s">
         <v>504</v>
       </c>
       <c r="N99" s="12">
         <v>23297018</v>
       </c>
-      <c r="O99" s="69" t="s">
+      <c r="O99" s="64" t="s">
         <v>505</v>
       </c>
-      <c r="P99" s="70">
+      <c r="P99" s="77">
         <v>14.241472</v>
       </c>
-      <c r="Q99" s="70">
+      <c r="Q99" s="77">
         <v>-90.255499999999998</v>
       </c>
       <c r="R99" s="14">
@@ -13067,16 +13102,16 @@
       <c r="U99" s="12">
         <v>180</v>
       </c>
-      <c r="V99" s="51" t="s">
+      <c r="V99" s="47" t="s">
         <v>506</v>
       </c>
-      <c r="W99" s="58" t="s">
+      <c r="W99" s="54" t="s">
         <v>507</v>
       </c>
-      <c r="X99" s="52">
+      <c r="X99" s="48">
         <v>744870.27</v>
       </c>
-      <c r="Y99" s="52">
+      <c r="Y99" s="48">
         <f>-253248.31+70968.18+104030.66-30295.01+23733.59+21475.76</f>
         <v>-63335.130000000005</v>
       </c>
@@ -13092,7 +13127,7 @@
         <v>148238.5</v>
       </c>
     </row>
-    <row r="100" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A100" s="7">
         <v>99</v>
       </c>
@@ -13105,16 +13140,16 @@
       <c r="D100" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E100" s="37" t="s">
+      <c r="E100" s="34" t="s">
         <v>508</v>
       </c>
-      <c r="F100" s="37" t="s">
+      <c r="F100" s="34" t="s">
         <v>509</v>
       </c>
-      <c r="G100" s="37" t="s">
+      <c r="G100" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="H100" s="38">
+      <c r="H100" s="35">
         <v>0.93</v>
       </c>
       <c r="I100" s="10">
@@ -13130,19 +13165,19 @@
       <c r="L100" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="M100" s="37" t="s">
+      <c r="M100" s="34" t="s">
         <v>504</v>
       </c>
       <c r="N100" s="12">
         <v>25023403</v>
       </c>
-      <c r="O100" s="69" t="s">
+      <c r="O100" s="64" t="s">
         <v>512</v>
       </c>
-      <c r="P100" s="70">
+      <c r="P100" s="77">
         <v>14.696888899999999</v>
       </c>
-      <c r="Q100" s="70">
+      <c r="Q100" s="77">
         <v>-91.795555555555495</v>
       </c>
       <c r="R100" s="14">
@@ -13157,16 +13192,16 @@
       <c r="U100" s="12">
         <v>120</v>
       </c>
-      <c r="V100" s="51" t="s">
+      <c r="V100" s="47" t="s">
         <v>513</v>
       </c>
-      <c r="W100" s="71" t="s">
+      <c r="W100" s="65" t="s">
         <v>514</v>
       </c>
-      <c r="X100" s="52">
+      <c r="X100" s="48">
         <v>1903913.31</v>
       </c>
-      <c r="Y100" s="52">
+      <c r="Y100" s="48">
         <f>-258085.91+392435.21+180107.45</f>
         <v>314456.75</v>
       </c>
@@ -13183,7 +13218,7 @@
         <v>1087222.1300000001</v>
       </c>
     </row>
-    <row r="101" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A101" s="7">
         <v>100</v>
       </c>
@@ -13196,16 +13231,16 @@
       <c r="D101" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E101" s="37" t="s">
+      <c r="E101" s="34" t="s">
         <v>515</v>
       </c>
-      <c r="F101" s="37" t="s">
+      <c r="F101" s="34" t="s">
         <v>509</v>
       </c>
-      <c r="G101" s="37" t="s">
+      <c r="G101" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="H101" s="38">
+      <c r="H101" s="35">
         <v>0.8</v>
       </c>
       <c r="I101" s="10">
@@ -13221,19 +13256,19 @@
       <c r="L101" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="M101" s="37" t="s">
+      <c r="M101" s="34" t="s">
         <v>504</v>
       </c>
       <c r="N101" s="12">
         <v>25078763</v>
       </c>
-      <c r="O101" s="69" t="s">
+      <c r="O101" s="64" t="s">
         <v>518</v>
       </c>
-      <c r="P101" s="70">
+      <c r="P101" s="77">
         <v>14.70026</v>
       </c>
-      <c r="Q101" s="70">
+      <c r="Q101" s="77">
         <v>-91.714877999999999</v>
       </c>
       <c r="R101" s="14">
@@ -13248,16 +13283,16 @@
       <c r="U101" s="12">
         <v>60</v>
       </c>
-      <c r="V101" s="51" t="s">
+      <c r="V101" s="47" t="s">
         <v>519</v>
       </c>
       <c r="W101" s="15" t="s">
         <v>520</v>
       </c>
-      <c r="X101" s="52">
+      <c r="X101" s="48">
         <v>3197904.65</v>
       </c>
-      <c r="Y101" s="52">
+      <c r="Y101" s="48">
         <f>-950043.38+279843.45+433934.52</f>
         <v>-236265.40999999992</v>
       </c>
@@ -13273,7 +13308,7 @@
         <v>1500511.4000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A102" s="7">
         <v>101</v>
       </c>
@@ -13286,16 +13321,16 @@
       <c r="D102" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E102" s="37" t="s">
+      <c r="E102" s="34" t="s">
         <v>521</v>
       </c>
-      <c r="F102" s="37" t="s">
+      <c r="F102" s="34" t="s">
         <v>509</v>
       </c>
-      <c r="G102" s="37" t="s">
+      <c r="G102" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="H102" s="38">
+      <c r="H102" s="35">
         <v>1</v>
       </c>
       <c r="I102" s="10">
@@ -13311,19 +13346,19 @@
       <c r="L102" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="M102" s="37" t="s">
+      <c r="M102" s="34" t="s">
         <v>504</v>
       </c>
       <c r="N102" s="12">
         <v>25078356</v>
       </c>
-      <c r="O102" s="69" t="s">
+      <c r="O102" s="64" t="s">
         <v>524</v>
       </c>
-      <c r="P102" s="70">
+      <c r="P102" s="77">
         <v>14.772833</v>
       </c>
-      <c r="Q102" s="70">
+      <c r="Q102" s="77">
         <v>-91.720072000000002</v>
       </c>
       <c r="R102" s="14">
@@ -13338,16 +13373,16 @@
       <c r="U102" s="12">
         <v>60</v>
       </c>
-      <c r="V102" s="51" t="s">
+      <c r="V102" s="47" t="s">
         <v>519</v>
       </c>
       <c r="W102" s="15" t="s">
         <v>520</v>
       </c>
-      <c r="X102" s="52">
+      <c r="X102" s="48">
         <v>1115361.42</v>
       </c>
-      <c r="Y102" s="52">
+      <c r="Y102" s="48">
         <f>-425483.64+68060.44+346165.08</f>
         <v>-11258.119999999995</v>
       </c>
@@ -13363,7 +13398,7 @@
         <v>803734.54999999981</v>
       </c>
     </row>
-    <row r="103" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
         <v>102</v>
       </c>
@@ -13376,16 +13411,16 @@
       <c r="D103" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E103" s="37" t="s">
+      <c r="E103" s="34" t="s">
         <v>525</v>
       </c>
-      <c r="F103" s="37" t="s">
+      <c r="F103" s="34" t="s">
         <v>526</v>
       </c>
-      <c r="G103" s="37" t="s">
+      <c r="G103" s="34" t="s">
         <v>527</v>
       </c>
-      <c r="H103" s="38">
+      <c r="H103" s="35">
         <v>1</v>
       </c>
       <c r="I103" s="10">
@@ -13401,19 +13436,19 @@
       <c r="L103" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="M103" s="37" t="s">
+      <c r="M103" s="34" t="s">
         <v>504</v>
       </c>
       <c r="N103" s="12">
         <v>25070193</v>
       </c>
-      <c r="O103" s="69" t="s">
+      <c r="O103" s="64" t="s">
         <v>530</v>
       </c>
-      <c r="P103" s="70">
+      <c r="P103" s="77">
         <v>15.088111100000001</v>
       </c>
-      <c r="Q103" s="70">
+      <c r="Q103" s="77">
         <v>-90.670221999999995</v>
       </c>
       <c r="R103" s="14">
@@ -13428,16 +13463,16 @@
       <c r="U103" s="12">
         <v>0</v>
       </c>
-      <c r="V103" s="51" t="s">
+      <c r="V103" s="47" t="s">
         <v>531</v>
       </c>
       <c r="W103" s="15" t="s">
         <v>532</v>
       </c>
-      <c r="X103" s="52">
+      <c r="X103" s="48">
         <v>1200000</v>
       </c>
-      <c r="Y103" s="52">
+      <c r="Y103" s="48">
         <f>-375666.77+108351.94+185570.46</f>
         <v>-81744.370000000024</v>
       </c>
@@ -13453,7 +13488,7 @@
         <v>223664.6399999999</v>
       </c>
     </row>
-    <row r="104" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A104" s="7">
         <v>103</v>
       </c>
@@ -13466,44 +13501,44 @@
       <c r="D104" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E104" s="37" t="s">
+      <c r="E104" s="34" t="s">
         <v>533</v>
       </c>
-      <c r="F104" s="37" t="s">
+      <c r="F104" s="34" t="s">
         <v>534</v>
       </c>
-      <c r="G104" s="37" t="s">
+      <c r="G104" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H104" s="38">
+      <c r="H104" s="35">
         <v>0.98080000000000001</v>
       </c>
       <c r="I104" s="10">
         <f t="shared" si="11"/>
         <v>0.79999999959988599</v>
       </c>
-      <c r="J104" s="72" t="s">
+      <c r="J104" s="66" t="s">
         <v>510</v>
       </c>
-      <c r="K104" s="72" t="s">
+      <c r="K104" s="66" t="s">
         <v>535</v>
       </c>
       <c r="L104" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="M104" s="37" t="s">
+      <c r="M104" s="34" t="s">
         <v>504</v>
       </c>
       <c r="N104" s="12">
         <v>25351893</v>
       </c>
-      <c r="O104" s="69" t="s">
+      <c r="O104" s="64" t="s">
         <v>536</v>
       </c>
-      <c r="P104" s="70">
+      <c r="P104" s="77">
         <v>14.644075000000001</v>
       </c>
-      <c r="Q104" s="70">
+      <c r="Q104" s="77">
         <v>-90.595890999999995</v>
       </c>
       <c r="R104" s="14">
@@ -13518,16 +13553,16 @@
       <c r="U104" s="12">
         <v>60</v>
       </c>
-      <c r="V104" s="51" t="s">
+      <c r="V104" s="47" t="s">
         <v>537</v>
       </c>
       <c r="W104" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="X104" s="52">
+      <c r="X104" s="48">
         <v>4195000</v>
       </c>
-      <c r="Y104" s="52">
+      <c r="Y104" s="48">
         <f>-181908.67+142107.21+843376.05</f>
         <v>803574.59000000008</v>
       </c>
@@ -13544,7 +13579,7 @@
         <v>999714.91999999993</v>
       </c>
     </row>
-    <row r="105" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
       <c r="A105" s="7">
         <v>104</v>
       </c>
@@ -13557,44 +13592,44 @@
       <c r="D105" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E105" s="37" t="s">
+      <c r="E105" s="34" t="s">
         <v>539</v>
       </c>
-      <c r="F105" s="37" t="s">
+      <c r="F105" s="34" t="s">
         <v>534</v>
       </c>
-      <c r="G105" s="37" t="s">
+      <c r="G105" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H105" s="38">
+      <c r="H105" s="35">
         <v>0.60499999999999998</v>
       </c>
       <c r="I105" s="10">
         <f t="shared" si="11"/>
         <v>0.37949365352199232</v>
       </c>
-      <c r="J105" s="73" t="s">
+      <c r="J105" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="K105" s="73" t="s">
+      <c r="K105" s="67" t="s">
         <v>540</v>
       </c>
       <c r="L105" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="M105" s="37" t="s">
+      <c r="M105" s="34" t="s">
         <v>504</v>
       </c>
       <c r="N105" s="12">
         <v>25077864</v>
       </c>
-      <c r="O105" s="69" t="s">
+      <c r="O105" s="64" t="s">
         <v>541</v>
       </c>
-      <c r="P105" s="70">
+      <c r="P105" s="77">
         <v>14.619365</v>
       </c>
-      <c r="Q105" s="70">
+      <c r="Q105" s="77">
         <v>-90.600774000000001</v>
       </c>
       <c r="R105" s="14">
@@ -13609,16 +13644,16 @@
       <c r="U105" s="12" t="s">
         <v>542</v>
       </c>
-      <c r="V105" s="51" t="s">
+      <c r="V105" s="47" t="s">
         <v>543</v>
       </c>
       <c r="W105" s="15" t="s">
         <v>544</v>
       </c>
-      <c r="X105" s="52">
+      <c r="X105" s="48">
         <v>7373495.04</v>
       </c>
-      <c r="Y105" s="52">
+      <c r="Y105" s="48">
         <f>-1578347.62+731594.6+2302919.87</f>
         <v>1456166.85</v>
       </c>
@@ -13635,7 +13670,7 @@
         <v>5478861.2400000002</v>
       </c>
     </row>
-    <row r="106" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A106" s="7">
         <v>105</v>
       </c>
@@ -13657,7 +13692,7 @@
       <c r="G106" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="H106" s="74">
+      <c r="H106" s="68">
         <v>0.93</v>
       </c>
       <c r="I106" s="10">
@@ -13673,19 +13708,19 @@
       <c r="L106" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="M106" s="37" t="s">
+      <c r="M106" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N106" s="75">
+      <c r="N106" s="69">
         <v>26285371</v>
       </c>
-      <c r="O106" s="72" t="s">
+      <c r="O106" s="66" t="s">
         <v>547</v>
       </c>
-      <c r="P106" s="70">
+      <c r="P106" s="77">
         <v>14.694638899999999</v>
       </c>
-      <c r="Q106" s="70">
+      <c r="Q106" s="77">
         <v>-91.7986111111111</v>
       </c>
       <c r="R106" s="14">
@@ -13700,16 +13735,16 @@
       <c r="U106" s="12">
         <v>45</v>
       </c>
-      <c r="V106" s="76" t="s">
+      <c r="V106" s="70" t="s">
         <v>513</v>
       </c>
-      <c r="W106" s="47" t="s">
+      <c r="W106" s="43" t="s">
         <v>514</v>
       </c>
-      <c r="X106" s="52">
+      <c r="X106" s="48">
         <v>880000</v>
       </c>
-      <c r="Y106" s="52">
+      <c r="Y106" s="48">
         <f>-509417.31+261717.6+363751.11</f>
         <v>116051.4</v>
       </c>
@@ -13725,7 +13760,7 @@
         <v>533340.41</v>
       </c>
     </row>
-    <row r="107" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A107" s="7">
         <v>106</v>
       </c>
@@ -13747,35 +13782,35 @@
       <c r="G107" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="H107" s="74">
+      <c r="H107" s="68">
         <v>0.92</v>
       </c>
       <c r="I107" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J107" s="72" t="s">
+      <c r="J107" s="66" t="s">
         <v>516</v>
       </c>
-      <c r="K107" s="72" t="s">
+      <c r="K107" s="66" t="s">
         <v>550</v>
       </c>
       <c r="L107" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="M107" s="37" t="s">
+      <c r="M107" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N107" s="75">
+      <c r="N107" s="69">
         <v>26285452</v>
       </c>
-      <c r="O107" s="72" t="s">
+      <c r="O107" s="66" t="s">
         <v>551</v>
       </c>
-      <c r="P107" s="70">
+      <c r="P107" s="77">
         <v>15.2295111</v>
       </c>
-      <c r="Q107" s="70">
+      <c r="Q107" s="77">
         <v>-91.390111111111096</v>
       </c>
       <c r="R107" s="14">
@@ -13790,16 +13825,16 @@
       <c r="U107" s="12">
         <v>60</v>
       </c>
-      <c r="V107" s="76" t="s">
+      <c r="V107" s="70" t="s">
         <v>552</v>
       </c>
-      <c r="W107" s="47" t="s">
+      <c r="W107" s="43" t="s">
         <v>553</v>
       </c>
-      <c r="X107" s="52">
+      <c r="X107" s="48">
         <v>860000</v>
       </c>
-      <c r="Y107" s="52">
+      <c r="Y107" s="48">
         <v>0</v>
       </c>
       <c r="Z107" s="18">
@@ -13814,7 +13849,7 @@
         <v>860000</v>
       </c>
     </row>
-    <row r="108" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A108" s="7">
         <v>107</v>
       </c>
@@ -13836,35 +13871,35 @@
       <c r="G108" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H108" s="74">
+      <c r="H108" s="68">
         <v>0.21149999999999999</v>
       </c>
       <c r="I108" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J108" s="72" t="s">
+      <c r="J108" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="K108" s="72" t="s">
+      <c r="K108" s="66" t="s">
         <v>556</v>
       </c>
       <c r="L108" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="M108" s="37" t="s">
+      <c r="M108" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N108" s="75">
+      <c r="N108" s="69">
         <v>26345137</v>
       </c>
-      <c r="O108" s="72" t="s">
+      <c r="O108" s="66" t="s">
         <v>557</v>
       </c>
-      <c r="P108" s="70">
+      <c r="P108" s="77">
         <v>14.3078056</v>
       </c>
-      <c r="Q108" s="70">
+      <c r="Q108" s="77">
         <v>-91.818722222222206</v>
       </c>
       <c r="R108" s="14">
@@ -13879,16 +13914,16 @@
       <c r="U108" s="12">
         <v>0</v>
       </c>
-      <c r="V108" s="76" t="s">
+      <c r="V108" s="70" t="s">
         <v>558</v>
       </c>
-      <c r="W108" s="47" t="s">
+      <c r="W108" s="43" t="s">
         <v>553</v>
       </c>
-      <c r="X108" s="52">
+      <c r="X108" s="48">
         <v>3375000</v>
       </c>
-      <c r="Y108" s="52">
+      <c r="Y108" s="48">
         <v>0</v>
       </c>
       <c r="Z108" s="18">
@@ -13903,7 +13938,7 @@
         <v>3375000</v>
       </c>
     </row>
-    <row r="109" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:28" ht="331.5" x14ac:dyDescent="0.25">
       <c r="A109" s="7">
         <v>108</v>
       </c>
@@ -13925,35 +13960,35 @@
       <c r="G109" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="H109" s="74">
+      <c r="H109" s="68">
         <v>0.499</v>
       </c>
       <c r="I109" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J109" s="72" t="s">
+      <c r="J109" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="K109" s="77" t="s">
+      <c r="K109" s="71" t="s">
         <v>560</v>
       </c>
       <c r="L109" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="M109" s="37" t="s">
+      <c r="M109" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N109" s="75">
+      <c r="N109" s="69">
         <v>26285541</v>
       </c>
-      <c r="O109" s="72" t="s">
+      <c r="O109" s="66" t="s">
         <v>561</v>
       </c>
-      <c r="P109" s="70">
+      <c r="P109" s="77">
         <v>15.46125</v>
       </c>
-      <c r="Q109" s="70">
+      <c r="Q109" s="77">
         <v>-90.694583333333298</v>
       </c>
       <c r="R109" s="14">
@@ -13968,16 +14003,16 @@
       <c r="U109" s="12">
         <v>40</v>
       </c>
-      <c r="V109" s="76" t="s">
+      <c r="V109" s="70" t="s">
         <v>558</v>
       </c>
-      <c r="W109" s="47" t="s">
+      <c r="W109" s="43" t="s">
         <v>553</v>
       </c>
-      <c r="X109" s="52">
+      <c r="X109" s="48">
         <v>1228000</v>
       </c>
-      <c r="Y109" s="52">
+      <c r="Y109" s="48">
         <v>0</v>
       </c>
       <c r="Z109" s="18">
@@ -13992,7 +14027,7 @@
         <v>1228000</v>
       </c>
     </row>
-    <row r="110" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A110" s="7">
         <v>109</v>
       </c>
@@ -14014,35 +14049,35 @@
       <c r="G110" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="H110" s="74">
+      <c r="H110" s="68">
         <v>0.8</v>
       </c>
       <c r="I110" s="10">
         <f t="shared" si="11"/>
         <v>0.23481302571274654</v>
       </c>
-      <c r="J110" s="72" t="s">
+      <c r="J110" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="K110" s="72" t="s">
+      <c r="K110" s="66" t="s">
         <v>564</v>
       </c>
       <c r="L110" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="M110" s="37" t="s">
+      <c r="M110" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N110" s="75">
+      <c r="N110" s="69">
         <v>26939495</v>
       </c>
-      <c r="O110" s="72" t="s">
+      <c r="O110" s="66" t="s">
         <v>565</v>
       </c>
-      <c r="P110" s="70">
+      <c r="P110" s="77">
         <v>14.962222199999999</v>
       </c>
-      <c r="Q110" s="70">
+      <c r="Q110" s="77">
         <v>-90.5266666666666</v>
       </c>
       <c r="R110" s="14">
@@ -14057,16 +14092,16 @@
       <c r="U110" s="12">
         <v>90</v>
       </c>
-      <c r="V110" s="76" t="s">
+      <c r="V110" s="70" t="s">
         <v>566</v>
       </c>
-      <c r="W110" s="47" t="s">
+      <c r="W110" s="43" t="s">
         <v>567</v>
       </c>
-      <c r="X110" s="52">
+      <c r="X110" s="48">
         <v>2035000</v>
       </c>
-      <c r="Y110" s="52">
+      <c r="Y110" s="48">
         <f>-505034.26+91056.3+258758.09</f>
         <v>-155219.87000000002</v>
       </c>
@@ -14082,7 +14117,7 @@
         <v>1438383.27</v>
       </c>
     </row>
-    <row r="111" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A111" s="7">
         <v>110</v>
       </c>
@@ -14104,35 +14139,35 @@
       <c r="G111" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="H111" s="74">
+      <c r="H111" s="68">
         <v>0.21</v>
       </c>
       <c r="I111" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J111" s="72" t="s">
+      <c r="J111" s="66" t="s">
         <v>571</v>
       </c>
-      <c r="K111" s="72" t="s">
+      <c r="K111" s="66" t="s">
         <v>572</v>
       </c>
       <c r="L111" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="M111" s="37" t="s">
+      <c r="M111" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N111" s="75">
+      <c r="N111" s="69">
         <v>26294419</v>
       </c>
-      <c r="O111" s="72" t="s">
+      <c r="O111" s="66" t="s">
         <v>573</v>
       </c>
-      <c r="P111" s="70">
+      <c r="P111" s="77">
         <v>14.584027799999999</v>
       </c>
-      <c r="Q111" s="70">
+      <c r="Q111" s="77">
         <v>-90.7394166666666</v>
       </c>
       <c r="R111" s="14">
@@ -14147,16 +14182,16 @@
       <c r="U111" s="12">
         <v>0</v>
       </c>
-      <c r="V111" s="76" t="s">
+      <c r="V111" s="70" t="s">
         <v>574</v>
       </c>
-      <c r="W111" s="47" t="s">
+      <c r="W111" s="43" t="s">
         <v>575</v>
       </c>
-      <c r="X111" s="52">
+      <c r="X111" s="48">
         <v>1285677</v>
       </c>
-      <c r="Y111" s="52">
+      <c r="Y111" s="48">
         <v>0</v>
       </c>
       <c r="Z111" s="18">
@@ -14171,7 +14206,7 @@
         <v>1285677</v>
       </c>
     </row>
-    <row r="112" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A112" s="7">
         <v>111</v>
       </c>
@@ -14193,35 +14228,35 @@
       <c r="G112" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H112" s="74">
+      <c r="H112" s="68">
         <v>0.4723</v>
       </c>
       <c r="I112" s="10">
         <f t="shared" si="11"/>
         <v>0.20003964764751961</v>
       </c>
-      <c r="J112" s="72" t="s">
+      <c r="J112" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="K112" s="72" t="s">
+      <c r="K112" s="66" t="s">
         <v>578</v>
       </c>
       <c r="L112" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M112" s="37" t="s">
+      <c r="M112" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N112" s="75">
+      <c r="N112" s="69">
         <v>26346869</v>
       </c>
-      <c r="O112" s="72" t="s">
+      <c r="O112" s="66" t="s">
         <v>579</v>
       </c>
-      <c r="P112" s="70">
+      <c r="P112" s="77">
         <v>14.306555599999999</v>
       </c>
-      <c r="Q112" s="70">
+      <c r="Q112" s="77">
         <v>-90.972388888888801</v>
       </c>
       <c r="R112" s="14">
@@ -14236,16 +14271,16 @@
       <c r="U112" s="12">
         <v>0</v>
       </c>
-      <c r="V112" s="76" t="s">
+      <c r="V112" s="70" t="s">
         <v>255</v>
       </c>
       <c r="W112" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="X112" s="52">
+      <c r="X112" s="48">
         <v>2298749.25</v>
       </c>
-      <c r="Y112" s="52">
+      <c r="Y112" s="48">
         <v>0</v>
       </c>
       <c r="Z112" s="18">
@@ -14260,7 +14295,7 @@
         <v>1838908.26</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" ht="234" x14ac:dyDescent="0.25">
       <c r="A113" s="7">
         <v>112</v>
       </c>
@@ -14282,35 +14317,35 @@
       <c r="G113" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H113" s="74">
+      <c r="H113" s="68">
         <v>0.26</v>
       </c>
       <c r="I113" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J113" s="72" t="s">
+      <c r="J113" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="K113" s="72" t="s">
+      <c r="K113" s="66" t="s">
         <v>581</v>
       </c>
       <c r="L113" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="M113" s="37" t="s">
+      <c r="M113" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N113" s="75">
+      <c r="N113" s="69">
         <v>26344475</v>
       </c>
-      <c r="O113" s="72" t="s">
+      <c r="O113" s="66" t="s">
         <v>582</v>
       </c>
-      <c r="P113" s="70">
+      <c r="P113" s="77">
         <v>14.320275000000001</v>
       </c>
-      <c r="Q113" s="70">
+      <c r="Q113" s="77">
         <v>-91.8986083333333</v>
       </c>
       <c r="R113" s="14">
@@ -14325,16 +14360,16 @@
       <c r="U113" s="12">
         <v>0</v>
       </c>
-      <c r="V113" s="76" t="s">
+      <c r="V113" s="70" t="s">
         <v>583</v>
       </c>
       <c r="W113" s="15" t="s">
         <v>584</v>
       </c>
-      <c r="X113" s="52">
+      <c r="X113" s="48">
         <v>2222136.59</v>
       </c>
-      <c r="Y113" s="52">
+      <c r="Y113" s="48">
         <v>0</v>
       </c>
       <c r="Z113" s="18">
@@ -14349,7 +14384,7 @@
         <v>2222136.59</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A114" s="7">
         <v>113</v>
       </c>
@@ -14371,34 +14406,34 @@
       <c r="G114" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H114" s="74">
+      <c r="H114" s="68">
         <v>0.2364</v>
       </c>
       <c r="I114" s="10">
         <v>0</v>
       </c>
-      <c r="J114" s="72" t="s">
+      <c r="J114" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="K114" s="72" t="s">
+      <c r="K114" s="66" t="s">
         <v>586</v>
       </c>
       <c r="L114" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="M114" s="37" t="s">
+      <c r="M114" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N114" s="75">
+      <c r="N114" s="69">
         <v>26975017</v>
       </c>
-      <c r="O114" s="72" t="s">
+      <c r="O114" s="66" t="s">
         <v>587</v>
       </c>
-      <c r="P114" s="70">
+      <c r="P114" s="77">
         <v>14.65</v>
       </c>
-      <c r="Q114" s="70">
+      <c r="Q114" s="77">
         <v>-90.660916388888893</v>
       </c>
       <c r="R114" s="14">
@@ -14413,16 +14448,16 @@
       <c r="U114" s="12">
         <v>0</v>
       </c>
-      <c r="V114" s="76" t="s">
+      <c r="V114" s="70" t="s">
         <v>588</v>
       </c>
       <c r="W114" s="15" t="s">
         <v>589</v>
       </c>
-      <c r="X114" s="52">
+      <c r="X114" s="48">
         <v>6750000</v>
       </c>
-      <c r="Y114" s="52">
+      <c r="Y114" s="48">
         <v>0</v>
       </c>
       <c r="Z114" s="18">
@@ -14437,7 +14472,7 @@
         <v>6750000</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" ht="253.5" x14ac:dyDescent="0.25">
       <c r="A115" s="7">
         <v>114</v>
       </c>
@@ -14459,34 +14494,34 @@
       <c r="G115" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="H115" s="74">
+      <c r="H115" s="68">
         <v>0.08</v>
       </c>
       <c r="I115" s="10">
         <v>0</v>
       </c>
-      <c r="J115" s="72" t="s">
+      <c r="J115" s="66" t="s">
         <v>592</v>
       </c>
-      <c r="K115" s="72" t="s">
+      <c r="K115" s="66" t="s">
         <v>593</v>
       </c>
       <c r="L115" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M115" s="37" t="s">
+      <c r="M115" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N115" s="75">
+      <c r="N115" s="69">
         <v>27655407</v>
       </c>
-      <c r="O115" s="72" t="s">
+      <c r="O115" s="66" t="s">
         <v>594</v>
       </c>
-      <c r="P115" s="70">
+      <c r="P115" s="77">
         <v>14.478433300000001</v>
       </c>
-      <c r="Q115" s="70">
+      <c r="Q115" s="77">
         <v>-90.808355555555494</v>
       </c>
       <c r="R115" s="14">
@@ -14501,16 +14536,16 @@
       <c r="U115" s="12">
         <v>0</v>
       </c>
-      <c r="V115" s="76" t="s">
+      <c r="V115" s="70" t="s">
         <v>595</v>
       </c>
       <c r="W115" s="15" t="s">
         <v>596</v>
       </c>
-      <c r="X115" s="52">
+      <c r="X115" s="48">
         <v>9400000</v>
       </c>
-      <c r="Y115" s="52">
+      <c r="Y115" s="48">
         <v>0</v>
       </c>
       <c r="Z115" s="18">
@@ -14525,7 +14560,7 @@
         <v>9400000</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A116" s="7">
         <v>115</v>
       </c>
@@ -14547,34 +14582,34 @@
       <c r="G116" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="H116" s="74">
+      <c r="H116" s="68">
         <v>0.13450000000000001</v>
       </c>
       <c r="I116" s="10">
         <v>0</v>
       </c>
-      <c r="J116" s="72" t="s">
+      <c r="J116" s="66" t="s">
         <v>598</v>
       </c>
-      <c r="K116" s="72" t="s">
+      <c r="K116" s="66" t="s">
         <v>599</v>
       </c>
       <c r="L116" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="M116" s="37" t="s">
+      <c r="M116" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N116" s="75">
+      <c r="N116" s="69">
         <v>27655423</v>
       </c>
-      <c r="O116" s="72" t="s">
+      <c r="O116" s="66" t="s">
         <v>600</v>
       </c>
-      <c r="P116" s="70">
+      <c r="P116" s="77">
         <v>14.975250000000001</v>
       </c>
-      <c r="Q116" s="70">
+      <c r="Q116" s="77">
         <v>-90.175389166666605</v>
       </c>
       <c r="R116" s="14">
@@ -14589,16 +14624,16 @@
       <c r="U116" s="12">
         <v>0</v>
       </c>
-      <c r="V116" s="76" t="s">
+      <c r="V116" s="70" t="s">
         <v>566</v>
       </c>
       <c r="W116" s="15" t="s">
         <v>567</v>
       </c>
-      <c r="X116" s="52">
+      <c r="X116" s="48">
         <v>1106000</v>
       </c>
-      <c r="Y116" s="52">
+      <c r="Y116" s="48">
         <v>0</v>
       </c>
       <c r="Z116" s="18">
@@ -14613,7 +14648,7 @@
         <v>1106000</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" ht="292.5" x14ac:dyDescent="0.25">
       <c r="A117" s="7">
         <v>116</v>
       </c>
@@ -14635,34 +14670,34 @@
       <c r="G117" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H117" s="74">
+      <c r="H117" s="68">
         <v>3.2300000000000002E-2</v>
       </c>
       <c r="I117" s="10">
         <v>0</v>
       </c>
-      <c r="J117" s="72" t="s">
+      <c r="J117" s="66" t="s">
         <v>603</v>
       </c>
-      <c r="K117" s="72" t="s">
+      <c r="K117" s="66" t="s">
         <v>604</v>
       </c>
       <c r="L117" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M117" s="37" t="s">
+      <c r="M117" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N117" s="75">
+      <c r="N117" s="69">
         <v>27655296</v>
       </c>
-      <c r="O117" s="72" t="s">
+      <c r="O117" s="66" t="s">
         <v>605</v>
       </c>
-      <c r="P117" s="70">
+      <c r="P117" s="77">
         <v>14.709166700000001</v>
       </c>
-      <c r="Q117" s="70">
+      <c r="Q117" s="77">
         <v>-90.550277777777694</v>
       </c>
       <c r="R117" s="14">
@@ -14677,16 +14712,16 @@
       <c r="U117" s="12">
         <v>0</v>
       </c>
-      <c r="V117" s="76" t="s">
+      <c r="V117" s="70" t="s">
         <v>583</v>
       </c>
       <c r="W117" s="15" t="s">
         <v>584</v>
       </c>
-      <c r="X117" s="52">
+      <c r="X117" s="48">
         <v>6260135</v>
       </c>
-      <c r="Y117" s="52">
+      <c r="Y117" s="48">
         <v>0</v>
       </c>
       <c r="Z117" s="18">
@@ -14701,7 +14736,7 @@
         <v>6260135</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" ht="117" x14ac:dyDescent="0.25">
       <c r="A118" s="7">
         <v>117</v>
       </c>
@@ -14723,34 +14758,34 @@
       <c r="G118" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="H118" s="74">
+      <c r="H118" s="68">
         <v>0</v>
       </c>
       <c r="I118" s="10">
         <v>0</v>
       </c>
-      <c r="J118" s="72" t="s">
+      <c r="J118" s="66" t="s">
         <v>608</v>
       </c>
-      <c r="K118" s="72" t="s">
+      <c r="K118" s="66" t="s">
         <v>609</v>
       </c>
       <c r="L118" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M118" s="37" t="s">
+      <c r="M118" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N118" s="75">
+      <c r="N118" s="69">
         <v>27773051</v>
       </c>
-      <c r="O118" s="72" t="s">
+      <c r="O118" s="66" t="s">
         <v>610</v>
       </c>
-      <c r="P118" s="70">
+      <c r="P118" s="77">
         <v>14.646894400000001</v>
       </c>
-      <c r="Q118" s="70">
+      <c r="Q118" s="77">
         <v>-90.725794444444404</v>
       </c>
       <c r="R118" s="14">
@@ -14765,16 +14800,16 @@
       <c r="U118" s="12">
         <v>0</v>
       </c>
-      <c r="V118" s="76" t="s">
+      <c r="V118" s="70" t="s">
         <v>595</v>
       </c>
       <c r="W118" s="15" t="s">
         <v>596</v>
       </c>
-      <c r="X118" s="52">
+      <c r="X118" s="48">
         <v>8910049.5</v>
       </c>
-      <c r="Y118" s="52">
+      <c r="Y118" s="48">
         <v>0</v>
       </c>
       <c r="Z118" s="18">
@@ -14789,7 +14824,7 @@
         <v>8910049.5</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A119" s="7">
         <v>118</v>
       </c>
@@ -14811,34 +14846,34 @@
       <c r="G119" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H119" s="74">
+      <c r="H119" s="68">
         <v>0.18</v>
       </c>
       <c r="I119" s="10">
         <v>0</v>
       </c>
-      <c r="J119" s="72" t="s">
+      <c r="J119" s="66" t="s">
         <v>612</v>
       </c>
-      <c r="K119" s="72" t="s">
+      <c r="K119" s="66" t="s">
         <v>613</v>
       </c>
       <c r="L119" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="M119" s="37" t="s">
+      <c r="M119" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N119" s="75">
+      <c r="N119" s="69">
         <v>27655474</v>
       </c>
-      <c r="O119" s="72" t="s">
+      <c r="O119" s="66" t="s">
         <v>614</v>
       </c>
-      <c r="P119" s="70">
+      <c r="P119" s="77">
         <v>14.7892417</v>
       </c>
-      <c r="Q119" s="70">
+      <c r="Q119" s="77">
         <v>-90.606341666666594</v>
       </c>
       <c r="R119" s="14">
@@ -14853,16 +14888,16 @@
       <c r="U119" s="12">
         <v>0</v>
       </c>
-      <c r="V119" s="76" t="s">
+      <c r="V119" s="70" t="s">
         <v>268</v>
       </c>
       <c r="W119" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="X119" s="52">
+      <c r="X119" s="48">
         <v>1099581</v>
       </c>
-      <c r="Y119" s="52">
+      <c r="Y119" s="48">
         <v>0</v>
       </c>
       <c r="Z119" s="18">
@@ -14877,7 +14912,7 @@
         <v>1099581</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" ht="273" x14ac:dyDescent="0.25">
       <c r="A120" s="7">
         <v>119</v>
       </c>
@@ -14899,34 +14934,34 @@
       <c r="G120" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H120" s="74">
+      <c r="H120" s="68">
         <v>0</v>
       </c>
       <c r="I120" s="10">
         <v>0</v>
       </c>
-      <c r="J120" s="72" t="s">
+      <c r="J120" s="66" t="s">
         <v>612</v>
       </c>
-      <c r="K120" s="72" t="s">
+      <c r="K120" s="66" t="s">
         <v>617</v>
       </c>
       <c r="L120" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M120" s="37" t="s">
+      <c r="M120" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N120" s="75">
+      <c r="N120" s="69">
         <v>27773116</v>
       </c>
-      <c r="O120" s="72" t="s">
+      <c r="O120" s="66" t="s">
         <v>618</v>
       </c>
-      <c r="P120" s="70">
+      <c r="P120" s="77">
         <v>14.7647222</v>
       </c>
-      <c r="Q120" s="70">
+      <c r="Q120" s="77">
         <v>-90.591666666666598</v>
       </c>
       <c r="R120" s="14">
@@ -14941,16 +14976,16 @@
       <c r="U120" s="12">
         <v>0</v>
       </c>
-      <c r="V120" s="76" t="s">
+      <c r="V120" s="70" t="s">
         <v>588</v>
       </c>
       <c r="W120" s="15" t="s">
         <v>589</v>
       </c>
-      <c r="X120" s="52">
+      <c r="X120" s="48">
         <v>11044868.529999999</v>
       </c>
-      <c r="Y120" s="52">
+      <c r="Y120" s="48">
         <v>0</v>
       </c>
       <c r="Z120" s="18">
@@ -14965,7 +15000,7 @@
         <v>11044868.529999999</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A121" s="7">
         <v>120</v>
       </c>
@@ -14987,34 +15022,34 @@
       <c r="G121" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H121" s="74">
+      <c r="H121" s="68">
         <v>0.01</v>
       </c>
       <c r="I121" s="10">
         <v>0</v>
       </c>
-      <c r="J121" s="72" t="s">
+      <c r="J121" s="66" t="s">
         <v>621</v>
       </c>
-      <c r="K121" s="72" t="s">
+      <c r="K121" s="66" t="s">
         <v>622</v>
       </c>
       <c r="L121" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="M121" s="37" t="s">
+      <c r="M121" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N121" s="75">
+      <c r="N121" s="69">
         <v>27773264</v>
       </c>
-      <c r="O121" s="72" t="s">
+      <c r="O121" s="66" t="s">
         <v>623</v>
       </c>
-      <c r="P121" s="70">
+      <c r="P121" s="77">
         <v>14.478222199999999</v>
       </c>
-      <c r="Q121" s="70">
+      <c r="Q121" s="77">
         <v>-90.615638888888796</v>
       </c>
       <c r="R121" s="14">
@@ -15029,16 +15064,16 @@
       <c r="U121" s="12">
         <v>0</v>
       </c>
-      <c r="V121" s="76" t="s">
+      <c r="V121" s="70" t="s">
         <v>583</v>
       </c>
       <c r="W121" s="15" t="s">
         <v>584</v>
       </c>
-      <c r="X121" s="52">
+      <c r="X121" s="48">
         <v>8582120</v>
       </c>
-      <c r="Y121" s="52">
+      <c r="Y121" s="48">
         <v>0</v>
       </c>
       <c r="Z121" s="18">
@@ -15053,7 +15088,7 @@
         <v>8582120</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" ht="136.5" x14ac:dyDescent="0.25">
       <c r="A122" s="7">
         <v>121</v>
       </c>
@@ -15075,34 +15110,34 @@
       <c r="G122" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H122" s="74">
+      <c r="H122" s="68">
         <v>0</v>
       </c>
       <c r="I122" s="10">
         <v>0</v>
       </c>
-      <c r="J122" s="72" t="s">
+      <c r="J122" s="66" t="s">
         <v>625</v>
       </c>
-      <c r="K122" s="72" t="s">
+      <c r="K122" s="66" t="s">
         <v>626</v>
       </c>
       <c r="L122" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="M122" s="37" t="s">
+      <c r="M122" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N122" s="75">
+      <c r="N122" s="69">
         <v>27655415</v>
       </c>
-      <c r="O122" s="72" t="s">
+      <c r="O122" s="66" t="s">
         <v>627</v>
       </c>
-      <c r="P122" s="70">
+      <c r="P122" s="77">
         <v>14.401460999999999</v>
       </c>
-      <c r="Q122" s="70">
+      <c r="Q122" s="77">
         <v>-90.697822000000002</v>
       </c>
       <c r="R122" s="14">
@@ -15117,16 +15152,16 @@
       <c r="U122" s="12">
         <v>0</v>
       </c>
-      <c r="V122" s="76" t="s">
+      <c r="V122" s="70" t="s">
         <v>583</v>
       </c>
       <c r="W122" s="15" t="s">
         <v>584</v>
       </c>
-      <c r="X122" s="52">
+      <c r="X122" s="48">
         <v>1271975</v>
       </c>
-      <c r="Y122" s="52">
+      <c r="Y122" s="48">
         <v>0</v>
       </c>
       <c r="Z122" s="18">
@@ -15141,7 +15176,7 @@
         <v>1271975</v>
       </c>
     </row>
-    <row r="123" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A123" s="7">
         <v>122</v>
       </c>
@@ -15163,34 +15198,34 @@
       <c r="G123" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H123" s="74">
+      <c r="H123" s="68">
         <v>0</v>
       </c>
       <c r="I123" s="10">
         <v>0</v>
       </c>
-      <c r="J123" s="72" t="s">
+      <c r="J123" s="66" t="s">
         <v>625</v>
       </c>
-      <c r="K123" s="72" t="s">
+      <c r="K123" s="66" t="s">
         <v>629</v>
       </c>
       <c r="L123" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M123" s="37" t="s">
+      <c r="M123" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N123" s="75">
+      <c r="N123" s="69">
         <v>27889823</v>
       </c>
-      <c r="O123" s="72" t="s">
+      <c r="O123" s="66" t="s">
         <v>630</v>
       </c>
-      <c r="P123" s="70">
+      <c r="P123" s="77">
         <v>14.232222</v>
       </c>
-      <c r="Q123" s="70">
+      <c r="Q123" s="77">
         <v>-90.731110999999999</v>
       </c>
       <c r="R123" s="14">
@@ -15205,16 +15240,16 @@
       <c r="U123" s="12">
         <v>0</v>
       </c>
-      <c r="V123" s="76" t="s">
+      <c r="V123" s="70" t="s">
         <v>583</v>
       </c>
       <c r="W123" s="15" t="s">
         <v>584</v>
       </c>
-      <c r="X123" s="52">
+      <c r="X123" s="48">
         <v>6752765</v>
       </c>
-      <c r="Y123" s="52">
+      <c r="Y123" s="48">
         <v>0</v>
       </c>
       <c r="Z123" s="18">
@@ -15229,7 +15264,7 @@
         <v>6752765</v>
       </c>
     </row>
-    <row r="124" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:28" ht="214.5" x14ac:dyDescent="0.25">
       <c r="A124" s="7">
         <v>123</v>
       </c>
@@ -15251,34 +15286,34 @@
       <c r="G124" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H124" s="74">
+      <c r="H124" s="68">
         <v>0</v>
       </c>
       <c r="I124" s="10">
         <v>0</v>
       </c>
-      <c r="J124" s="72" t="s">
+      <c r="J124" s="66" t="s">
         <v>633</v>
       </c>
-      <c r="K124" s="72" t="s">
+      <c r="K124" s="66" t="s">
         <v>634</v>
       </c>
       <c r="L124" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="M124" s="37" t="s">
+      <c r="M124" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N124" s="75">
+      <c r="N124" s="69">
         <v>27945693</v>
       </c>
-      <c r="O124" s="72" t="s">
+      <c r="O124" s="66" t="s">
         <v>635</v>
       </c>
-      <c r="P124" s="70">
+      <c r="P124" s="77">
         <v>14.507111</v>
       </c>
-      <c r="Q124" s="70">
+      <c r="Q124" s="77">
         <v>-90.566055000000006</v>
       </c>
       <c r="R124" s="14">
@@ -15293,16 +15328,16 @@
       <c r="U124" s="12">
         <v>0</v>
       </c>
-      <c r="V124" s="76" t="s">
+      <c r="V124" s="70" t="s">
         <v>268</v>
       </c>
       <c r="W124" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="X124" s="52">
+      <c r="X124" s="48">
         <v>11890047.9</v>
       </c>
-      <c r="Y124" s="52">
+      <c r="Y124" s="48">
         <v>0</v>
       </c>
       <c r="Z124" s="18">
@@ -15317,7 +15352,7 @@
         <v>11890047.9</v>
       </c>
     </row>
-    <row r="125" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A125" s="7">
         <v>124</v>
       </c>
@@ -15339,34 +15374,34 @@
       <c r="G125" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="H125" s="74">
+      <c r="H125" s="68">
         <v>7.1400000000000005E-2</v>
       </c>
       <c r="I125" s="10">
         <v>0</v>
       </c>
-      <c r="J125" s="72" t="s">
+      <c r="J125" s="66" t="s">
         <v>638</v>
       </c>
-      <c r="K125" s="72" t="s">
+      <c r="K125" s="66" t="s">
         <v>639</v>
       </c>
       <c r="L125" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="M125" s="37" t="s">
+      <c r="M125" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N125" s="75">
+      <c r="N125" s="69">
         <v>27630099</v>
       </c>
-      <c r="O125" s="72" t="s">
+      <c r="O125" s="66" t="s">
         <v>640</v>
       </c>
-      <c r="P125" s="70">
+      <c r="P125" s="77">
         <v>15.362056259999999</v>
       </c>
-      <c r="Q125" s="70">
+      <c r="Q125" s="77">
         <v>-89.294705680000007</v>
       </c>
       <c r="R125" s="14">
@@ -15381,16 +15416,16 @@
       <c r="U125" s="12">
         <v>0</v>
       </c>
-      <c r="V125" s="51" t="s">
+      <c r="V125" s="47" t="s">
         <v>537</v>
       </c>
       <c r="W125" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="X125" s="52">
+      <c r="X125" s="48">
         <v>10654361.800000001</v>
       </c>
-      <c r="Y125" s="52">
+      <c r="Y125" s="48">
         <v>0</v>
       </c>
       <c r="Z125" s="18">
@@ -15405,7 +15440,7 @@
         <v>10654361.800000001</v>
       </c>
     </row>
-    <row r="126" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A126" s="7">
         <v>125</v>
       </c>
@@ -15427,34 +15462,34 @@
       <c r="G126" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="H126" s="74">
+      <c r="H126" s="68">
         <v>7.6899999999999996E-2</v>
       </c>
       <c r="I126" s="10">
         <v>0</v>
       </c>
-      <c r="J126" s="72" t="s">
+      <c r="J126" s="66" t="s">
         <v>642</v>
       </c>
-      <c r="K126" s="72" t="s">
+      <c r="K126" s="66" t="s">
         <v>643</v>
       </c>
       <c r="L126" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="M126" s="37" t="s">
+      <c r="M126" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N126" s="75">
+      <c r="N126" s="69">
         <v>27630285</v>
       </c>
-      <c r="O126" s="72" t="s">
+      <c r="O126" s="66" t="s">
         <v>644</v>
       </c>
-      <c r="P126" s="70">
+      <c r="P126" s="77">
         <v>15.306975</v>
       </c>
-      <c r="Q126" s="70">
+      <c r="Q126" s="77">
         <v>-89.459366666666597</v>
       </c>
       <c r="R126" s="14">
@@ -15469,16 +15504,16 @@
       <c r="U126" s="12">
         <v>0</v>
       </c>
-      <c r="V126" s="51" t="s">
+      <c r="V126" s="47" t="s">
         <v>537</v>
       </c>
       <c r="W126" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="X126" s="52">
+      <c r="X126" s="48">
         <v>4882264.96</v>
       </c>
-      <c r="Y126" s="52">
+      <c r="Y126" s="48">
         <v>0</v>
       </c>
       <c r="Z126" s="18">
@@ -15493,7 +15528,7 @@
         <v>4882264.96</v>
       </c>
     </row>
-    <row r="127" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:28" ht="117" x14ac:dyDescent="0.25">
       <c r="A127" s="7">
         <v>126</v>
       </c>
@@ -15515,34 +15550,34 @@
       <c r="G127" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="H127" s="74">
+      <c r="H127" s="68">
         <v>0.1</v>
       </c>
       <c r="I127" s="10">
         <v>0</v>
       </c>
-      <c r="J127" s="72" t="s">
+      <c r="J127" s="66" t="s">
         <v>642</v>
       </c>
-      <c r="K127" s="72" t="s">
+      <c r="K127" s="66" t="s">
         <v>646</v>
       </c>
       <c r="L127" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="M127" s="37" t="s">
+      <c r="M127" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N127" s="75">
+      <c r="N127" s="69">
         <v>27629783</v>
       </c>
-      <c r="O127" s="72" t="s">
+      <c r="O127" s="66" t="s">
         <v>647</v>
       </c>
-      <c r="P127" s="70">
+      <c r="P127" s="77">
         <v>15.61548</v>
       </c>
-      <c r="Q127" s="70">
+      <c r="Q127" s="77">
         <v>-89.191747000000007</v>
       </c>
       <c r="R127" s="14">
@@ -15557,16 +15592,16 @@
       <c r="U127" s="12">
         <v>0</v>
       </c>
-      <c r="V127" s="51" t="s">
+      <c r="V127" s="47" t="s">
         <v>537</v>
       </c>
       <c r="W127" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="X127" s="52">
+      <c r="X127" s="48">
         <v>4744595.2</v>
       </c>
-      <c r="Y127" s="52">
+      <c r="Y127" s="48">
         <v>0</v>
       </c>
       <c r="Z127" s="18">
@@ -15581,7 +15616,7 @@
         <v>4744595.2</v>
       </c>
     </row>
-    <row r="128" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:28" ht="156" x14ac:dyDescent="0.25">
       <c r="A128" s="7">
         <v>127</v>
       </c>
@@ -15603,34 +15638,34 @@
       <c r="G128" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="H128" s="74">
+      <c r="H128" s="68">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I128" s="10">
         <v>0</v>
       </c>
-      <c r="J128" s="72" t="s">
+      <c r="J128" s="66" t="s">
         <v>649</v>
       </c>
-      <c r="K128" s="72" t="s">
+      <c r="K128" s="66" t="s">
         <v>650</v>
       </c>
       <c r="L128" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="M128" s="37" t="s">
+      <c r="M128" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N128" s="75">
+      <c r="N128" s="69">
         <v>27630234</v>
       </c>
-      <c r="O128" s="72" t="s">
+      <c r="O128" s="66" t="s">
         <v>651</v>
       </c>
-      <c r="P128" s="70">
+      <c r="P128" s="77">
         <v>15.588081389999999</v>
       </c>
-      <c r="Q128" s="70">
+      <c r="Q128" s="77">
         <v>-89.204860550000006</v>
       </c>
       <c r="R128" s="14">
@@ -15645,16 +15680,16 @@
       <c r="U128" s="12">
         <v>0</v>
       </c>
-      <c r="V128" s="51" t="s">
+      <c r="V128" s="47" t="s">
         <v>537</v>
       </c>
       <c r="W128" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="X128" s="52">
+      <c r="X128" s="48">
         <v>4587910.5999999996</v>
       </c>
-      <c r="Y128" s="52">
+      <c r="Y128" s="48">
         <v>0</v>
       </c>
       <c r="Z128" s="18">
@@ -15669,7 +15704,7 @@
         <v>4587910.5999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:28" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A129" s="7">
         <v>128</v>
       </c>
@@ -15691,34 +15726,34 @@
       <c r="G129" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="H129" s="74">
+      <c r="H129" s="68">
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="I129" s="10">
         <v>0</v>
       </c>
-      <c r="J129" s="72" t="s">
+      <c r="J129" s="66" t="s">
         <v>649</v>
       </c>
-      <c r="K129" s="72" t="s">
+      <c r="K129" s="66" t="s">
         <v>653</v>
       </c>
       <c r="L129" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="M129" s="37" t="s">
+      <c r="M129" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="N129" s="75">
+      <c r="N129" s="69">
         <v>27630137</v>
       </c>
-      <c r="O129" s="72" t="s">
+      <c r="O129" s="66" t="s">
         <v>654</v>
       </c>
-      <c r="P129" s="70">
+      <c r="P129" s="77">
         <v>15.3307222</v>
       </c>
-      <c r="Q129" s="70">
+      <c r="Q129" s="77">
         <v>-89.371305555555494</v>
       </c>
       <c r="R129" s="14">
@@ -15733,16 +15768,16 @@
       <c r="U129" s="12">
         <v>0</v>
       </c>
-      <c r="V129" s="51" t="s">
+      <c r="V129" s="47" t="s">
         <v>537</v>
       </c>
       <c r="W129" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="X129" s="52">
+      <c r="X129" s="48">
         <v>4117616</v>
       </c>
-      <c r="Y129" s="52">
+      <c r="Y129" s="48">
         <v>0</v>
       </c>
       <c r="Z129" s="18">
@@ -15758,6 +15793,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AB129" xr:uid="{A11FCA36-68E1-48DB-B35D-1906B0292A5D}"/>
   <mergeCells count="18">
     <mergeCell ref="K84:K87"/>
     <mergeCell ref="K88:K89"/>
